--- a/experiments/敦煌变化数据_predicted.xlsx
+++ b/experiments/敦煌变化数据_predicted.xlsx
@@ -6842,20 +6842,14 @@
           <t>5.12</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>7.16</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-3.91</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3.59</t>
-        </is>
+      <c r="B9" s="23" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>37.39</v>
+      </c>
+      <c r="D9" s="23" t="n">
+        <v>22.12</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>

--- a/experiments/敦煌变化数据_predicted.xlsx
+++ b/experiments/敦煌变化数据_predicted.xlsx
@@ -77,7 +77,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -106,6 +106,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFE9D6"/>
         <bgColor rgb="00FFE9D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3E5F5"/>
+        <bgColor rgb="00F3E5F5"/>
       </patternFill>
     </fill>
   </fills>
@@ -182,7 +188,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -252,6 +258,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10395,139 +10407,139 @@
       <c r="A4" s="3" t="n">
         <v>4.17</v>
       </c>
-      <c r="B4" s="11" t="n">
+      <c r="B4" s="25" t="n">
         <v>47.45</v>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="25" t="n">
         <v>35.56</v>
       </c>
-      <c r="D4" s="11" t="n">
+      <c r="D4" s="25" t="n">
         <v>18.73</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="25" t="n">
         <v>46.45</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="25" t="n">
         <v>36.05</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="H4" s="11" t="n">
+      <c r="H4" s="25" t="n">
         <v>48.16</v>
       </c>
-      <c r="I4" s="11" t="n">
+      <c r="I4" s="25" t="n">
         <v>35.74</v>
       </c>
-      <c r="J4" s="11" t="n">
+      <c r="J4" s="25" t="n">
         <v>19.65</v>
       </c>
-      <c r="K4" s="11" t="n">
+      <c r="K4" s="25" t="n">
         <v>59.82</v>
       </c>
-      <c r="L4" s="11" t="n">
+      <c r="L4" s="25" t="n">
         <v>-31.73</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" s="25" t="n">
         <v>15.24</v>
       </c>
-      <c r="N4" s="11" t="n">
+      <c r="N4" s="25" t="n">
         <v>59.27</v>
       </c>
-      <c r="O4" s="11" t="n">
+      <c r="O4" s="25" t="n">
         <v>-32.38</v>
       </c>
-      <c r="P4" s="11" t="n">
+      <c r="P4" s="25" t="n">
         <v>14.74</v>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="25" t="n">
         <v>58.98</v>
       </c>
-      <c r="R4" s="11" t="n">
+      <c r="R4" s="25" t="n">
         <v>-32.05</v>
       </c>
-      <c r="S4" s="11" t="n">
+      <c r="S4" s="25" t="n">
         <v>15.98</v>
       </c>
-      <c r="T4" s="11" t="n">
+      <c r="T4" s="25" t="n">
         <v>41.4</v>
       </c>
-      <c r="U4" s="11" t="n">
+      <c r="U4" s="25" t="n">
         <v>-5.3</v>
       </c>
-      <c r="V4" s="11" t="n">
+      <c r="V4" s="25" t="n">
         <v>-32.75</v>
       </c>
-      <c r="W4" s="11" t="n">
+      <c r="W4" s="25" t="n">
         <v>40.51</v>
       </c>
-      <c r="X4" s="11" t="n">
+      <c r="X4" s="25" t="n">
         <v>-4.94</v>
       </c>
-      <c r="Y4" s="11" t="n">
+      <c r="Y4" s="25" t="n">
         <v>-33.11</v>
       </c>
-      <c r="Z4" s="11" t="n">
+      <c r="Z4" s="25" t="n">
         <v>40.61</v>
       </c>
-      <c r="AA4" s="11" t="n">
+      <c r="AA4" s="25" t="n">
         <v>-5.44</v>
       </c>
-      <c r="AB4" s="11" t="n">
+      <c r="AB4" s="25" t="n">
         <v>-32.22</v>
       </c>
-      <c r="AC4" s="11" t="n">
+      <c r="AC4" s="25" t="n">
         <v>49.2</v>
       </c>
-      <c r="AD4" s="11" t="n">
+      <c r="AD4" s="25" t="n">
         <v>36.1</v>
       </c>
-      <c r="AE4" s="11" t="n">
+      <c r="AE4" s="25" t="n">
         <v>22.25</v>
       </c>
-      <c r="AF4" s="11" t="n">
+      <c r="AF4" s="25" t="n">
         <v>51.68</v>
       </c>
-      <c r="AG4" s="11" t="n">
+      <c r="AG4" s="25" t="n">
         <v>34.77</v>
       </c>
-      <c r="AH4" s="11" t="n">
+      <c r="AH4" s="25" t="n">
         <v>21.18</v>
       </c>
-      <c r="AI4" s="11" t="n">
+      <c r="AI4" s="25" t="n">
         <v>59.81</v>
       </c>
-      <c r="AJ4" s="11" t="n">
+      <c r="AJ4" s="25" t="n">
         <v>-32.16</v>
       </c>
-      <c r="AK4" s="11" t="n">
+      <c r="AK4" s="25" t="n">
         <v>15.73</v>
       </c>
-      <c r="AL4" s="11" t="n">
+      <c r="AL4" s="25" t="n">
         <v>62.84</v>
       </c>
-      <c r="AM4" s="11" t="n">
+      <c r="AM4" s="25" t="n">
         <v>-30.47</v>
       </c>
-      <c r="AN4" s="11" t="n">
+      <c r="AN4" s="25" t="n">
         <v>13.9</v>
       </c>
-      <c r="AO4" s="11" t="n">
+      <c r="AO4" s="25" t="n">
         <v>41.17</v>
       </c>
-      <c r="AP4" s="11" t="n">
+      <c r="AP4" s="25" t="n">
         <v>-4.12</v>
       </c>
-      <c r="AQ4" s="11" t="n">
+      <c r="AQ4" s="25" t="n">
         <v>-28.95</v>
       </c>
-      <c r="AR4" s="11" t="n">
+      <c r="AR4" s="25" t="n">
         <v>39.08</v>
       </c>
-      <c r="AS4" s="11" t="n">
+      <c r="AS4" s="25" t="n">
         <v>-6.04</v>
       </c>
-      <c r="AT4" s="11" t="n">
+      <c r="AT4" s="25" t="n">
         <v>-28.25</v>
       </c>
     </row>
@@ -10537,140 +10549,140 @@
           <t>4.20</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="26" t="n">
         <v>45.67</v>
       </c>
-      <c r="C5" s="12" t="n">
+      <c r="C5" s="26" t="n">
         <v>33.99</v>
       </c>
-      <c r="D5" s="12" t="n">
-        <v>16.21</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>45.23</v>
-      </c>
-      <c r="F5" s="12" t="n">
+      <c r="D5" s="26" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>46.97</v>
+      </c>
+      <c r="F5" s="26" t="n">
         <v>37.01</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="26" t="n">
         <v>16.01</v>
       </c>
-      <c r="H5" s="12" t="n">
-        <v>45.79</v>
-      </c>
-      <c r="I5" s="12" t="n">
+      <c r="H5" s="26" t="n">
+        <v>48.11</v>
+      </c>
+      <c r="I5" s="26" t="n">
         <v>34.47</v>
       </c>
-      <c r="J5" s="12" t="n">
-        <v>15.85</v>
-      </c>
-      <c r="K5" s="12" t="n">
+      <c r="J5" s="26" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="K5" s="26" t="n">
         <v>58.69</v>
       </c>
-      <c r="L5" s="12" t="n">
+      <c r="L5" s="26" t="n">
         <v>-32.46</v>
       </c>
-      <c r="M5" s="12" t="n">
+      <c r="M5" s="26" t="n">
         <v>15.24</v>
       </c>
-      <c r="N5" s="12" t="n">
+      <c r="N5" s="26" t="n">
         <v>57.49</v>
       </c>
-      <c r="O5" s="12" t="n">
+      <c r="O5" s="26" t="n">
         <v>-31.79</v>
       </c>
-      <c r="P5" s="12" t="n">
+      <c r="P5" s="26" t="n">
         <v>16.64</v>
       </c>
-      <c r="Q5" s="12" t="n">
+      <c r="Q5" s="26" t="n">
         <v>62.69</v>
       </c>
-      <c r="R5" s="12" t="n">
-        <v>-26.17</v>
-      </c>
-      <c r="S5" s="12" t="n">
+      <c r="R5" s="26" t="n">
+        <v>-32.05</v>
+      </c>
+      <c r="S5" s="26" t="n">
         <v>10.62</v>
       </c>
-      <c r="T5" s="12" t="n">
+      <c r="T5" s="26" t="n">
         <v>40.37</v>
       </c>
-      <c r="U5" s="12" t="n">
+      <c r="U5" s="26" t="n">
         <v>-5.07</v>
       </c>
-      <c r="V5" s="12" t="n">
+      <c r="V5" s="26" t="n">
         <v>-33.27</v>
       </c>
-      <c r="W5" s="12" t="n">
+      <c r="W5" s="26" t="n">
         <v>40.18</v>
       </c>
-      <c r="X5" s="12" t="n">
+      <c r="X5" s="26" t="n">
         <v>-6.11</v>
       </c>
-      <c r="Y5" s="12" t="n">
+      <c r="Y5" s="26" t="n">
         <v>-31.11</v>
       </c>
-      <c r="Z5" s="12" t="n">
+      <c r="Z5" s="26" t="n">
         <v>40.96</v>
       </c>
-      <c r="AA5" s="12" t="n">
+      <c r="AA5" s="26" t="n">
         <v>-5.21</v>
       </c>
-      <c r="AB5" s="12" t="n">
+      <c r="AB5" s="26" t="n">
         <v>-33.07</v>
       </c>
-      <c r="AC5" s="12" t="n">
+      <c r="AC5" s="26" t="n">
         <v>47.69</v>
       </c>
-      <c r="AD5" s="12" t="n">
+      <c r="AD5" s="26" t="n">
         <v>34.29</v>
       </c>
-      <c r="AE5" s="12" t="n">
+      <c r="AE5" s="26" t="n">
         <v>19.1</v>
       </c>
-      <c r="AF5" s="12" t="n">
+      <c r="AF5" s="26" t="n">
         <v>49.49</v>
       </c>
-      <c r="AG5" s="12" t="n">
+      <c r="AG5" s="26" t="n">
         <v>34.86</v>
       </c>
-      <c r="AH5" s="12" t="n">
+      <c r="AH5" s="26" t="n">
         <v>18.86</v>
       </c>
-      <c r="AI5" s="12" t="n">
+      <c r="AI5" s="26" t="n">
         <v>61.53</v>
       </c>
-      <c r="AJ5" s="12" t="n">
+      <c r="AJ5" s="26" t="n">
         <v>-30.89</v>
       </c>
-      <c r="AK5" s="12" t="n">
+      <c r="AK5" s="26" t="n">
         <v>15.43</v>
       </c>
-      <c r="AL5" s="12" t="n">
+      <c r="AL5" s="26" t="n">
         <v>62.7</v>
       </c>
-      <c r="AM5" s="12" t="n">
+      <c r="AM5" s="26" t="n">
         <v>-30.91</v>
       </c>
-      <c r="AN5" s="12" t="n">
+      <c r="AN5" s="26" t="n">
         <v>14.18</v>
       </c>
-      <c r="AO5" s="12" t="n">
+      <c r="AO5" s="26" t="n">
         <v>37.81</v>
       </c>
-      <c r="AP5" s="12" t="n">
+      <c r="AP5" s="26" t="n">
         <v>-7.22</v>
       </c>
-      <c r="AQ5" s="12" t="n">
+      <c r="AQ5" s="26" t="n">
         <v>-28.06</v>
       </c>
-      <c r="AR5" s="12" t="n">
+      <c r="AR5" s="26" t="n">
         <v>39.08</v>
       </c>
-      <c r="AS5" s="12" t="n">
+      <c r="AS5" s="26" t="n">
         <v>-7.15</v>
       </c>
-      <c r="AT5" s="12" t="n">
-        <v>-19.75</v>
+      <c r="AT5" s="26" t="n">
+        <v>-27.36</v>
       </c>
     </row>
     <row r="6">
@@ -10679,139 +10691,139 @@
           <t>4.23</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
-        <v>46.02</v>
-      </c>
-      <c r="C6" s="12" t="n">
+      <c r="B6" s="26" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="C6" s="26" t="n">
         <v>32.95</v>
       </c>
-      <c r="D6" s="12" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>44.71</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>29.07</v>
-      </c>
-      <c r="G6" s="12" t="n">
+      <c r="D6" s="26" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>36.03</v>
+      </c>
+      <c r="G6" s="26" t="n">
         <v>16.11</v>
       </c>
-      <c r="H6" s="12" t="n">
-        <v>46.12</v>
-      </c>
-      <c r="I6" s="12" t="n">
+      <c r="H6" s="26" t="n">
+        <v>47.86</v>
+      </c>
+      <c r="I6" s="26" t="n">
         <v>33.56</v>
       </c>
-      <c r="J6" s="12" t="n">
+      <c r="J6" s="26" t="n">
         <v>16.93</v>
       </c>
-      <c r="K6" s="12" t="n">
+      <c r="K6" s="26" t="n">
         <v>59.23</v>
       </c>
-      <c r="L6" s="12" t="n">
+      <c r="L6" s="26" t="n">
         <v>-31.9</v>
       </c>
-      <c r="M6" s="12" t="n">
+      <c r="M6" s="26" t="n">
         <v>16.16</v>
       </c>
-      <c r="N6" s="12" t="n">
+      <c r="N6" s="26" t="n">
         <v>58.38</v>
       </c>
-      <c r="O6" s="12" t="n">
+      <c r="O6" s="26" t="n">
         <v>-32.83</v>
       </c>
-      <c r="P6" s="12" t="n">
+      <c r="P6" s="26" t="n">
         <v>16.34</v>
       </c>
-      <c r="Q6" s="12" t="n">
+      <c r="Q6" s="26" t="n">
         <v>60.62</v>
       </c>
-      <c r="R6" s="12" t="n">
+      <c r="R6" s="26" t="n">
         <v>-32.96</v>
       </c>
-      <c r="S6" s="12" t="n">
+      <c r="S6" s="26" t="n">
         <v>15.41</v>
       </c>
-      <c r="T6" s="12" t="n">
+      <c r="T6" s="26" t="n">
         <v>40.79</v>
       </c>
-      <c r="U6" s="12" t="n">
+      <c r="U6" s="26" t="n">
         <v>-5.98</v>
       </c>
-      <c r="V6" s="12" t="n">
+      <c r="V6" s="26" t="n">
         <v>-31.71</v>
       </c>
-      <c r="W6" s="12" t="n">
+      <c r="W6" s="26" t="n">
         <v>40.23</v>
       </c>
-      <c r="X6" s="12" t="n">
+      <c r="X6" s="26" t="n">
         <v>-5.38</v>
       </c>
-      <c r="Y6" s="12" t="n">
+      <c r="Y6" s="26" t="n">
         <v>-32.33</v>
       </c>
-      <c r="Z6" s="12" t="n">
+      <c r="Z6" s="26" t="n">
         <v>40.17</v>
       </c>
-      <c r="AA6" s="12" t="n">
+      <c r="AA6" s="26" t="n">
         <v>-5.16</v>
       </c>
-      <c r="AB6" s="12" t="n">
+      <c r="AB6" s="26" t="n">
         <v>-33.39</v>
       </c>
-      <c r="AC6" s="12" t="n">
+      <c r="AC6" s="26" t="n">
         <v>48.66</v>
       </c>
-      <c r="AD6" s="12" t="n">
+      <c r="AD6" s="26" t="n">
         <v>34.13</v>
       </c>
-      <c r="AE6" s="12" t="n">
+      <c r="AE6" s="26" t="n">
         <v>21.01</v>
       </c>
-      <c r="AF6" s="12" t="n">
+      <c r="AF6" s="26" t="n">
         <v>49.7</v>
       </c>
-      <c r="AG6" s="12" t="n">
+      <c r="AG6" s="26" t="n">
         <v>34.58</v>
       </c>
-      <c r="AH6" s="12" t="n">
+      <c r="AH6" s="26" t="n">
         <v>18.97</v>
       </c>
-      <c r="AI6" s="12" t="n">
+      <c r="AI6" s="26" t="n">
         <v>60.23</v>
       </c>
-      <c r="AJ6" s="12" t="n">
+      <c r="AJ6" s="26" t="n">
         <v>-31.05</v>
       </c>
-      <c r="AK6" s="12" t="n">
+      <c r="AK6" s="26" t="n">
         <v>14.58</v>
       </c>
-      <c r="AL6" s="12" t="n">
+      <c r="AL6" s="26" t="n">
         <v>62.65</v>
       </c>
-      <c r="AM6" s="12" t="n">
-        <v>-12.22</v>
-      </c>
-      <c r="AN6" s="12" t="n">
+      <c r="AM6" s="26" t="n">
+        <v>-30.8</v>
+      </c>
+      <c r="AN6" s="26" t="n">
         <v>14.14</v>
       </c>
-      <c r="AO6" s="12" t="n">
+      <c r="AO6" s="26" t="n">
         <v>37.57</v>
       </c>
-      <c r="AP6" s="12" t="n">
+      <c r="AP6" s="26" t="n">
         <v>-6.38</v>
       </c>
-      <c r="AQ6" s="12" t="n">
+      <c r="AQ6" s="26" t="n">
         <v>-28.08</v>
       </c>
-      <c r="AR6" s="12" t="n">
+      <c r="AR6" s="26" t="n">
         <v>39.52</v>
       </c>
-      <c r="AS6" s="12" t="n">
+      <c r="AS6" s="26" t="n">
         <v>-8.44</v>
       </c>
-      <c r="AT6" s="12" t="n">
+      <c r="AT6" s="26" t="n">
         <v>-27.36</v>
       </c>
     </row>
@@ -10821,139 +10833,139 @@
           <t>4.26</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
-        <v>49.03</v>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>24.23</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>21.53</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>44.88</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>33.91</v>
-      </c>
-      <c r="G7" s="12" t="n">
+      <c r="B7" s="26" t="n">
+        <v>45.55</v>
+      </c>
+      <c r="C7" s="26" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>18.05</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>46.62</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>37.39</v>
+      </c>
+      <c r="G7" s="26" t="n">
         <v>16.42</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="26" t="n">
         <v>46.38</v>
       </c>
-      <c r="I7" s="12" t="n">
+      <c r="I7" s="26" t="n">
         <v>33.79</v>
       </c>
-      <c r="J7" s="12" t="n">
+      <c r="J7" s="26" t="n">
         <v>15.47</v>
       </c>
-      <c r="K7" s="12" t="n">
+      <c r="K7" s="26" t="n">
         <v>58.65</v>
       </c>
-      <c r="L7" s="12" t="n">
+      <c r="L7" s="26" t="n">
         <v>-30.63</v>
       </c>
-      <c r="M7" s="12" t="n">
+      <c r="M7" s="26" t="n">
         <v>14.77</v>
       </c>
-      <c r="N7" s="12" t="n">
+      <c r="N7" s="26" t="n">
         <v>57.58</v>
       </c>
-      <c r="O7" s="12" t="n">
+      <c r="O7" s="26" t="n">
         <v>-33.2</v>
       </c>
-      <c r="P7" s="12" t="n">
+      <c r="P7" s="26" t="n">
         <v>16.79</v>
       </c>
-      <c r="Q7" s="12" t="n">
+      <c r="Q7" s="26" t="n">
         <v>60.76</v>
       </c>
-      <c r="R7" s="12" t="n">
+      <c r="R7" s="26" t="n">
         <v>-31.01</v>
       </c>
-      <c r="S7" s="12" t="n">
+      <c r="S7" s="26" t="n">
         <v>9.82</v>
       </c>
-      <c r="T7" s="12" t="n">
+      <c r="T7" s="26" t="n">
         <v>38.89</v>
       </c>
-      <c r="U7" s="12" t="n">
+      <c r="U7" s="26" t="n">
         <v>-4.71</v>
       </c>
-      <c r="V7" s="12" t="n">
+      <c r="V7" s="26" t="n">
         <v>-33.74</v>
       </c>
-      <c r="W7" s="12" t="n">
+      <c r="W7" s="26" t="n">
         <v>40.23</v>
       </c>
-      <c r="X7" s="12" t="n">
+      <c r="X7" s="26" t="n">
         <v>-5.44</v>
       </c>
-      <c r="Y7" s="12" t="n">
+      <c r="Y7" s="26" t="n">
         <v>-32.2</v>
       </c>
-      <c r="Z7" s="12" t="n">
+      <c r="Z7" s="26" t="n">
         <v>40.64</v>
       </c>
-      <c r="AA7" s="12" t="n">
+      <c r="AA7" s="26" t="n">
         <v>-5.58</v>
       </c>
-      <c r="AB7" s="12" t="n">
+      <c r="AB7" s="26" t="n">
         <v>-33.04</v>
       </c>
-      <c r="AC7" s="12" t="n">
+      <c r="AC7" s="26" t="n">
         <v>47.74</v>
       </c>
-      <c r="AD7" s="12" t="n">
+      <c r="AD7" s="26" t="n">
         <v>34.76</v>
       </c>
-      <c r="AE7" s="12" t="n">
+      <c r="AE7" s="26" t="n">
         <v>20.28</v>
       </c>
-      <c r="AF7" s="12" t="n">
+      <c r="AF7" s="26" t="n">
         <v>49.68</v>
       </c>
-      <c r="AG7" s="12" t="n">
+      <c r="AG7" s="26" t="n">
         <v>32.32</v>
       </c>
-      <c r="AH7" s="12" t="n">
+      <c r="AH7" s="26" t="n">
         <v>18.25</v>
       </c>
-      <c r="AI7" s="12" t="n">
+      <c r="AI7" s="26" t="n">
         <v>61.24</v>
       </c>
-      <c r="AJ7" s="12" t="n">
+      <c r="AJ7" s="26" t="n">
         <v>-30.68</v>
       </c>
-      <c r="AK7" s="12" t="n">
+      <c r="AK7" s="26" t="n">
         <v>15.19</v>
       </c>
-      <c r="AL7" s="12" t="n">
+      <c r="AL7" s="26" t="n">
         <v>62.63</v>
       </c>
-      <c r="AM7" s="12" t="n">
+      <c r="AM7" s="26" t="n">
         <v>-30.8</v>
       </c>
-      <c r="AN7" s="12" t="n">
+      <c r="AN7" s="26" t="n">
         <v>14.54</v>
       </c>
-      <c r="AO7" s="12" t="n">
+      <c r="AO7" s="26" t="n">
         <v>39.81</v>
       </c>
-      <c r="AP7" s="12" t="n">
+      <c r="AP7" s="26" t="n">
         <v>-6.07</v>
       </c>
-      <c r="AQ7" s="12" t="n">
+      <c r="AQ7" s="26" t="n">
         <v>-26.79</v>
       </c>
-      <c r="AR7" s="12" t="n">
+      <c r="AR7" s="26" t="n">
         <v>37.1</v>
       </c>
-      <c r="AS7" s="12" t="n">
+      <c r="AS7" s="26" t="n">
         <v>-6.68</v>
       </c>
-      <c r="AT7" s="12" t="n">
+      <c r="AT7" s="26" t="n">
         <v>-28.69</v>
       </c>
     </row>
@@ -10963,139 +10975,139 @@
           <t>4.29</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="26" t="n">
         <v>46.49</v>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="26" t="n">
         <v>33.44</v>
       </c>
-      <c r="D8" s="12" t="n">
-        <v>16.28</v>
-      </c>
-      <c r="E8" s="12" t="n">
+      <c r="D8" s="26" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="E8" s="26" t="n">
         <v>45.58</v>
       </c>
-      <c r="F8" s="12" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="G8" s="12" t="n">
+      <c r="F8" s="26" t="n">
+        <v>36.38</v>
+      </c>
+      <c r="G8" s="26" t="n">
         <v>16.16</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="26" t="n">
         <v>46.8</v>
       </c>
-      <c r="I8" s="12" t="n">
+      <c r="I8" s="26" t="n">
         <v>33.67</v>
       </c>
-      <c r="J8" s="12" t="n">
+      <c r="J8" s="26" t="n">
         <v>14.36</v>
       </c>
-      <c r="K8" s="12" t="n">
+      <c r="K8" s="26" t="n">
         <v>59.66</v>
       </c>
-      <c r="L8" s="12" t="n">
+      <c r="L8" s="26" t="n">
         <v>-30.96</v>
       </c>
-      <c r="M8" s="12" t="n">
+      <c r="M8" s="26" t="n">
         <v>15</v>
       </c>
-      <c r="N8" s="12" t="n">
+      <c r="N8" s="26" t="n">
         <v>57.7</v>
       </c>
-      <c r="O8" s="12" t="n">
+      <c r="O8" s="26" t="n">
         <v>-32.36</v>
       </c>
-      <c r="P8" s="12" t="n">
+      <c r="P8" s="26" t="n">
         <v>15.52</v>
       </c>
-      <c r="Q8" s="12" t="n">
+      <c r="Q8" s="26" t="n">
         <v>57.69</v>
       </c>
-      <c r="R8" s="12" t="n">
+      <c r="R8" s="26" t="n">
         <v>-31.89</v>
       </c>
-      <c r="S8" s="12" t="n">
+      <c r="S8" s="26" t="n">
         <v>14.01</v>
       </c>
-      <c r="T8" s="12" t="n">
+      <c r="T8" s="26" t="n">
         <v>43.07</v>
       </c>
-      <c r="U8" s="12" t="n">
+      <c r="U8" s="26" t="n">
         <v>-5.61</v>
       </c>
-      <c r="V8" s="12" t="n">
+      <c r="V8" s="26" t="n">
         <v>-29.58</v>
       </c>
-      <c r="W8" s="12" t="n">
+      <c r="W8" s="26" t="n">
         <v>41.01</v>
       </c>
-      <c r="X8" s="12" t="n">
+      <c r="X8" s="26" t="n">
         <v>-4.63</v>
       </c>
-      <c r="Y8" s="12" t="n">
+      <c r="Y8" s="26" t="n">
         <v>-33.2</v>
       </c>
-      <c r="Z8" s="12" t="n">
+      <c r="Z8" s="26" t="n">
         <v>42.04</v>
       </c>
-      <c r="AA8" s="12" t="n">
+      <c r="AA8" s="26" t="n">
         <v>-4.29</v>
       </c>
-      <c r="AB8" s="12" t="n">
+      <c r="AB8" s="26" t="n">
         <v>-33.3</v>
       </c>
-      <c r="AC8" s="12" t="n">
+      <c r="AC8" s="26" t="n">
         <v>49.39</v>
       </c>
-      <c r="AD8" s="12" t="n">
+      <c r="AD8" s="26" t="n">
         <v>31.28</v>
       </c>
-      <c r="AE8" s="12" t="n">
+      <c r="AE8" s="26" t="n">
         <v>16.38</v>
       </c>
-      <c r="AF8" s="12" t="n">
+      <c r="AF8" s="26" t="n">
         <v>50.58</v>
       </c>
-      <c r="AG8" s="12" t="n">
+      <c r="AG8" s="26" t="n">
         <v>31.76</v>
       </c>
-      <c r="AH8" s="12" t="n">
+      <c r="AH8" s="26" t="n">
         <v>17.4</v>
       </c>
-      <c r="AI8" s="12" t="n">
+      <c r="AI8" s="26" t="n">
         <v>62.87</v>
       </c>
-      <c r="AJ8" s="12" t="n">
+      <c r="AJ8" s="26" t="n">
         <v>-30.56</v>
       </c>
-      <c r="AK8" s="12" t="n">
+      <c r="AK8" s="26" t="n">
         <v>14.46</v>
       </c>
-      <c r="AL8" s="12" t="n">
+      <c r="AL8" s="26" t="n">
         <v>62.56</v>
       </c>
-      <c r="AM8" s="12" t="n">
+      <c r="AM8" s="26" t="n">
         <v>-31.08</v>
       </c>
-      <c r="AN8" s="12" t="n">
+      <c r="AN8" s="26" t="n">
         <v>14.58</v>
       </c>
-      <c r="AO8" s="12" t="n">
+      <c r="AO8" s="26" t="n">
         <v>41.57</v>
       </c>
-      <c r="AP8" s="12" t="n">
+      <c r="AP8" s="26" t="n">
         <v>-8.51</v>
       </c>
-      <c r="AQ8" s="12" t="n">
+      <c r="AQ8" s="26" t="n">
         <v>-23.67</v>
       </c>
-      <c r="AR8" s="12" t="n">
+      <c r="AR8" s="26" t="n">
         <v>33</v>
       </c>
-      <c r="AS8" s="12" t="n">
+      <c r="AS8" s="26" t="n">
         <v>-6.58</v>
       </c>
-      <c r="AT8" s="12" t="n">
+      <c r="AT8" s="26" t="n">
         <v>-30.37</v>
       </c>
     </row>
@@ -11105,139 +11117,139 @@
           <t>5.12</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
-        <v>46.88</v>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>32.36</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>15.11</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>46.43</v>
-      </c>
-      <c r="F9" s="12" t="n">
+      <c r="B9" s="26" t="n">
+        <v>46.51</v>
+      </c>
+      <c r="C9" s="26" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>45.39</v>
+      </c>
+      <c r="F9" s="26" t="n">
         <v>34.69</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="26" t="n">
         <v>16.02</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="H9" s="26" t="n">
         <v>46.7</v>
       </c>
-      <c r="I9" s="12" t="n">
-        <v>37.38</v>
-      </c>
-      <c r="J9" s="12" t="n">
+      <c r="I9" s="26" t="n">
+        <v>33.89</v>
+      </c>
+      <c r="J9" s="26" t="n">
         <v>15.21</v>
       </c>
-      <c r="K9" s="12" t="n">
+      <c r="K9" s="26" t="n">
         <v>59.84</v>
       </c>
-      <c r="L9" s="12" t="n">
+      <c r="L9" s="26" t="n">
         <v>-31.9</v>
       </c>
-      <c r="M9" s="12" t="n">
+      <c r="M9" s="26" t="n">
         <v>15.31</v>
       </c>
-      <c r="N9" s="12" t="n">
+      <c r="N9" s="26" t="n">
         <v>58.38</v>
       </c>
-      <c r="O9" s="12" t="n">
+      <c r="O9" s="26" t="n">
         <v>-32.99</v>
       </c>
-      <c r="P9" s="12" t="n">
+      <c r="P9" s="26" t="n">
         <v>16.66</v>
       </c>
-      <c r="Q9" s="12" t="n">
+      <c r="Q9" s="26" t="n">
         <v>62.27</v>
       </c>
-      <c r="R9" s="12" t="n">
+      <c r="R9" s="26" t="n">
         <v>-28.15</v>
       </c>
-      <c r="S9" s="12" t="n">
+      <c r="S9" s="26" t="n">
         <v>18.47</v>
       </c>
-      <c r="T9" s="12" t="n">
+      <c r="T9" s="26" t="n">
         <v>41.28</v>
       </c>
-      <c r="U9" s="12" t="n">
+      <c r="U9" s="26" t="n">
         <v>-5.65</v>
       </c>
-      <c r="V9" s="12" t="n">
+      <c r="V9" s="26" t="n">
         <v>-32.66</v>
       </c>
-      <c r="W9" s="12" t="n">
+      <c r="W9" s="26" t="n">
         <v>41.28</v>
       </c>
-      <c r="X9" s="12" t="n">
+      <c r="X9" s="26" t="n">
         <v>-5.79</v>
       </c>
-      <c r="Y9" s="12" t="n">
+      <c r="Y9" s="26" t="n">
         <v>-31.93</v>
       </c>
-      <c r="Z9" s="12" t="n">
+      <c r="Z9" s="26" t="n">
         <v>41.25</v>
       </c>
-      <c r="AA9" s="12" t="n">
+      <c r="AA9" s="26" t="n">
         <v>-3.77</v>
       </c>
-      <c r="AB9" s="12" t="n">
+      <c r="AB9" s="26" t="n">
         <v>-34.92</v>
       </c>
-      <c r="AC9" s="12" t="n">
+      <c r="AC9" s="26" t="n">
         <v>49.91</v>
       </c>
-      <c r="AD9" s="12" t="n">
+      <c r="AD9" s="26" t="n">
         <v>31.89</v>
       </c>
-      <c r="AE9" s="12" t="n">
+      <c r="AE9" s="26" t="n">
         <v>15.56</v>
       </c>
-      <c r="AF9" s="12" t="n">
+      <c r="AF9" s="26" t="n">
         <v>50.95</v>
       </c>
-      <c r="AG9" s="12" t="n">
+      <c r="AG9" s="26" t="n">
         <v>33.52</v>
       </c>
-      <c r="AH9" s="12" t="n">
+      <c r="AH9" s="26" t="n">
         <v>18.46</v>
       </c>
-      <c r="AI9" s="12" t="n">
+      <c r="AI9" s="26" t="n">
         <v>62.44</v>
       </c>
-      <c r="AJ9" s="12" t="n">
+      <c r="AJ9" s="26" t="n">
         <v>-29.06</v>
       </c>
-      <c r="AK9" s="12" t="n">
+      <c r="AK9" s="26" t="n">
         <v>11.93</v>
       </c>
-      <c r="AL9" s="12" t="n">
+      <c r="AL9" s="26" t="n">
         <v>63</v>
       </c>
-      <c r="AM9" s="12" t="n">
+      <c r="AM9" s="26" t="n">
         <v>-30.16</v>
       </c>
-      <c r="AN9" s="12" t="n">
+      <c r="AN9" s="26" t="n">
         <v>13.85</v>
       </c>
-      <c r="AO9" s="12" t="n">
+      <c r="AO9" s="26" t="n">
         <v>38.4</v>
       </c>
-      <c r="AP9" s="12" t="n">
+      <c r="AP9" s="26" t="n">
         <v>-7.03</v>
       </c>
-      <c r="AQ9" s="12" t="n">
+      <c r="AQ9" s="26" t="n">
         <v>-27.61</v>
       </c>
-      <c r="AR9" s="12" t="n">
+      <c r="AR9" s="26" t="n">
         <v>39.97</v>
       </c>
-      <c r="AS9" s="12" t="n">
+      <c r="AS9" s="26" t="n">
         <v>-6.93</v>
       </c>
-      <c r="AT9" s="12" t="n">
+      <c r="AT9" s="26" t="n">
         <v>-29.54</v>
       </c>
     </row>
@@ -11247,137 +11259,139 @@
           <t>5.14</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
-        <v>46.67</v>
-      </c>
-      <c r="C10" s="12" t="n">
+      <c r="B10" s="26" t="n">
+        <v>46.47</v>
+      </c>
+      <c r="C10" s="26" t="n">
         <v>33.71</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="26" t="n">
         <v>16.36</v>
       </c>
-      <c r="E10" s="12" t="n">
-        <v>46.08</v>
-      </c>
-      <c r="F10" s="12" t="n">
+      <c r="E10" s="26" t="n">
+        <v>45.37</v>
+      </c>
+      <c r="F10" s="26" t="n">
         <v>33.19</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="26" t="n">
         <v>15.36</v>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" s="26" t="n">
         <v>47.27</v>
       </c>
-      <c r="I10" s="12" t="n">
+      <c r="I10" s="26" t="n">
         <v>33.51</v>
       </c>
-      <c r="J10" s="12" t="n">
+      <c r="J10" s="26" t="n">
         <v>15.31</v>
       </c>
-      <c r="K10" s="12" t="n">
+      <c r="K10" s="26" t="n">
         <v>60.97</v>
       </c>
-      <c r="L10" s="12" t="n">
+      <c r="L10" s="26" t="n">
         <v>-31.29</v>
       </c>
-      <c r="M10" s="12" t="n">
+      <c r="M10" s="26" t="n">
         <v>13.48</v>
       </c>
-      <c r="N10" s="12" t="n">
+      <c r="N10" s="26" t="n">
         <v>58.28</v>
       </c>
-      <c r="O10" s="12" t="n">
+      <c r="O10" s="26" t="n">
         <v>-32.38</v>
       </c>
-      <c r="P10" s="12" t="n">
+      <c r="P10" s="26" t="n">
         <v>15.98</v>
       </c>
-      <c r="Q10" s="12" t="n">
+      <c r="Q10" s="26" t="n">
         <v>61.8</v>
       </c>
-      <c r="R10" s="12" t="n">
+      <c r="R10" s="26" t="n">
         <v>-28.93</v>
       </c>
-      <c r="S10" s="12" t="n">
+      <c r="S10" s="26" t="n">
         <v>12.32</v>
       </c>
-      <c r="T10" s="12" t="n">
+      <c r="T10" s="26" t="n">
         <v>45.04</v>
       </c>
-      <c r="U10" s="12" t="n">
+      <c r="U10" s="26" t="n">
         <v>-6.57</v>
       </c>
-      <c r="V10" s="12" t="n">
+      <c r="V10" s="26" t="n">
         <v>-27.23</v>
       </c>
-      <c r="W10" s="12" t="n">
+      <c r="W10" s="26" t="n">
         <v>41.24</v>
       </c>
-      <c r="X10" s="12" t="n">
+      <c r="X10" s="26" t="n">
         <v>-4.37</v>
       </c>
-      <c r="Y10" s="12" t="n">
+      <c r="Y10" s="26" t="n">
         <v>-33.88</v>
       </c>
-      <c r="Z10" s="12" t="n">
+      <c r="Z10" s="26" t="n">
         <v>41.06</v>
       </c>
-      <c r="AA10" s="12" t="n">
+      <c r="AA10" s="26" t="n">
         <v>-5</v>
       </c>
-      <c r="AB10" s="12" t="n">
+      <c r="AB10" s="26" t="n">
         <v>-34.61</v>
       </c>
-      <c r="AC10" s="12" t="n">
+      <c r="AC10" s="26" t="n">
         <v>50.18</v>
       </c>
-      <c r="AD10" s="13" t="n"/>
-      <c r="AE10" s="12" t="n">
+      <c r="AD10" s="26" t="n">
+        <v>29.21</v>
+      </c>
+      <c r="AE10" s="26" t="n">
         <v>16.05</v>
       </c>
-      <c r="AF10" s="12" t="n">
+      <c r="AF10" s="26" t="n">
         <v>51.02</v>
       </c>
-      <c r="AG10" s="12" t="n">
+      <c r="AG10" s="26" t="n">
         <v>33.43</v>
       </c>
-      <c r="AH10" s="12" t="n">
+      <c r="AH10" s="26" t="n">
         <v>18.15</v>
       </c>
-      <c r="AI10" s="12" t="n">
+      <c r="AI10" s="26" t="n">
         <v>59.51</v>
       </c>
-      <c r="AJ10" s="12" t="n">
+      <c r="AJ10" s="26" t="n">
         <v>-28.4</v>
       </c>
-      <c r="AK10" s="12" t="n">
+      <c r="AK10" s="26" t="n">
         <v>11.2</v>
       </c>
-      <c r="AL10" s="12" t="n">
+      <c r="AL10" s="26" t="n">
         <v>63</v>
       </c>
-      <c r="AM10" s="12" t="n">
+      <c r="AM10" s="26" t="n">
         <v>-30.7</v>
       </c>
-      <c r="AN10" s="12" t="n">
+      <c r="AN10" s="26" t="n">
         <v>15.52</v>
       </c>
-      <c r="AO10" s="12" t="n">
+      <c r="AO10" s="26" t="n">
         <v>42.15</v>
       </c>
-      <c r="AP10" s="12" t="n">
+      <c r="AP10" s="26" t="n">
         <v>-7.76</v>
       </c>
-      <c r="AQ10" s="12" t="n">
+      <c r="AQ10" s="26" t="n">
         <v>-23.81</v>
       </c>
-      <c r="AR10" s="12" t="n">
+      <c r="AR10" s="26" t="n">
         <v>40.39</v>
       </c>
-      <c r="AS10" s="12" t="n">
+      <c r="AS10" s="26" t="n">
         <v>-7.45</v>
       </c>
-      <c r="AT10" s="12" t="n">
+      <c r="AT10" s="26" t="n">
         <v>-28.56</v>
       </c>
     </row>
@@ -11387,139 +11401,139 @@
           <t>5.18</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="26" t="n">
         <v>46.63</v>
       </c>
-      <c r="C11" s="12" t="n">
-        <v>34.72</v>
-      </c>
-      <c r="D11" s="12" t="n">
+      <c r="C11" s="26" t="n">
+        <v>32.98</v>
+      </c>
+      <c r="D11" s="26" t="n">
         <v>16</v>
       </c>
-      <c r="E11" s="12" t="n">
-        <v>46.03</v>
-      </c>
-      <c r="F11" s="12" t="n">
+      <c r="E11" s="26" t="n">
+        <v>44.29</v>
+      </c>
+      <c r="F11" s="26" t="n">
         <v>34.07</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="26" t="n">
         <v>15.5</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="H11" s="26" t="n">
         <v>46.73</v>
       </c>
-      <c r="I11" s="12" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="J11" s="12" t="n">
+      <c r="I11" s="26" t="n">
+        <v>33.55</v>
+      </c>
+      <c r="J11" s="26" t="n">
         <v>14.81</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="K11" s="26" t="n">
         <v>61.21</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="L11" s="26" t="n">
         <v>-31.17</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="M11" s="26" t="n">
         <v>16.27</v>
       </c>
-      <c r="N11" s="12" t="n">
+      <c r="N11" s="26" t="n">
         <v>58.68</v>
       </c>
-      <c r="O11" s="12" t="n">
+      <c r="O11" s="26" t="n">
         <v>-31.7</v>
       </c>
-      <c r="P11" s="12" t="n">
+      <c r="P11" s="26" t="n">
         <v>17.13</v>
       </c>
-      <c r="Q11" s="12" t="n">
+      <c r="Q11" s="26" t="n">
         <v>60.44</v>
       </c>
-      <c r="R11" s="12" t="n">
+      <c r="R11" s="26" t="n">
         <v>-29.33</v>
       </c>
-      <c r="S11" s="12" t="n">
+      <c r="S11" s="26" t="n">
         <v>15.02</v>
       </c>
-      <c r="T11" s="12" t="n">
+      <c r="T11" s="26" t="n">
         <v>46.69</v>
       </c>
-      <c r="U11" s="12" t="n">
+      <c r="U11" s="26" t="n">
         <v>-7.95</v>
       </c>
-      <c r="V11" s="12" t="n">
+      <c r="V11" s="26" t="n">
         <v>-30.8</v>
       </c>
-      <c r="W11" s="12" t="n">
+      <c r="W11" s="26" t="n">
         <v>40.7</v>
       </c>
-      <c r="X11" s="12" t="n">
+      <c r="X11" s="26" t="n">
         <v>-4.24</v>
       </c>
-      <c r="Y11" s="12" t="n">
+      <c r="Y11" s="26" t="n">
         <v>-34.54</v>
       </c>
-      <c r="Z11" s="12" t="n">
+      <c r="Z11" s="26" t="n">
         <v>42.02</v>
       </c>
-      <c r="AA11" s="12" t="n">
+      <c r="AA11" s="26" t="n">
         <v>-5.82</v>
       </c>
-      <c r="AB11" s="12" t="n">
+      <c r="AB11" s="26" t="n">
         <v>-31.68</v>
       </c>
-      <c r="AC11" s="12" t="n">
+      <c r="AC11" s="26" t="n">
         <v>50.44</v>
       </c>
-      <c r="AD11" s="12" t="n">
+      <c r="AD11" s="26" t="n">
         <v>29.21</v>
       </c>
-      <c r="AE11" s="12" t="n">
+      <c r="AE11" s="26" t="n">
         <v>12.5</v>
       </c>
-      <c r="AF11" s="12" t="n">
+      <c r="AF11" s="26" t="n">
         <v>50.5</v>
       </c>
-      <c r="AG11" s="12" t="n">
+      <c r="AG11" s="26" t="n">
         <v>34.25</v>
       </c>
-      <c r="AH11" s="12" t="n">
+      <c r="AH11" s="26" t="n">
         <v>18.73</v>
       </c>
-      <c r="AI11" s="12" t="n">
+      <c r="AI11" s="26" t="n">
         <v>62.26</v>
       </c>
-      <c r="AJ11" s="12" t="n">
+      <c r="AJ11" s="26" t="n">
         <v>-27.76</v>
       </c>
-      <c r="AK11" s="12" t="n">
+      <c r="AK11" s="26" t="n">
         <v>11.41</v>
       </c>
-      <c r="AL11" s="12" t="n">
+      <c r="AL11" s="26" t="n">
         <v>62.82</v>
       </c>
-      <c r="AM11" s="12" t="n">
+      <c r="AM11" s="26" t="n">
         <v>-30.38</v>
       </c>
-      <c r="AN11" s="12" t="n">
+      <c r="AN11" s="26" t="n">
         <v>14.09</v>
       </c>
-      <c r="AO11" s="12" t="n">
+      <c r="AO11" s="26" t="n">
         <v>39.92</v>
       </c>
-      <c r="AP11" s="12" t="n">
+      <c r="AP11" s="26" t="n">
         <v>-7.36</v>
       </c>
-      <c r="AQ11" s="12" t="n">
+      <c r="AQ11" s="26" t="n">
         <v>-26.72</v>
       </c>
-      <c r="AR11" s="12" t="n">
+      <c r="AR11" s="26" t="n">
         <v>40.39</v>
       </c>
-      <c r="AS11" s="12" t="n">
+      <c r="AS11" s="26" t="n">
         <v>-8.27</v>
       </c>
-      <c r="AT11" s="12" t="n">
+      <c r="AT11" s="26" t="n">
         <v>-27.21</v>
       </c>
     </row>
@@ -11529,139 +11543,139 @@
           <t>5.21</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="26" t="n">
         <v>46.44</v>
       </c>
-      <c r="C12" s="12" t="n">
-        <v>33.99</v>
-      </c>
-      <c r="D12" s="12" t="n">
+      <c r="C12" s="26" t="n">
+        <v>32.86</v>
+      </c>
+      <c r="D12" s="26" t="n">
         <v>15.79</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="26" t="n">
         <v>45.2</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="26" t="n">
         <v>33.89</v>
       </c>
-      <c r="G12" s="12" t="n">
-        <v>16.46</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>47.64</v>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>34.76</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>17.13</v>
-      </c>
-      <c r="K12" s="12" t="n">
+      <c r="G12" s="26" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="H12" s="26" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>33.37</v>
+      </c>
+      <c r="J12" s="26" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="K12" s="26" t="n">
         <v>60.39</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="L12" s="26" t="n">
         <v>-31.89</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="M12" s="26" t="n">
         <v>15.24</v>
       </c>
-      <c r="N12" s="12" t="n">
+      <c r="N12" s="26" t="n">
         <v>57.3</v>
       </c>
-      <c r="O12" s="12" t="n">
+      <c r="O12" s="26" t="n">
         <v>-31.27</v>
       </c>
-      <c r="P12" s="12" t="n">
+      <c r="P12" s="26" t="n">
         <v>16.52</v>
       </c>
-      <c r="Q12" s="12" t="n">
+      <c r="Q12" s="26" t="n">
         <v>59.42</v>
       </c>
-      <c r="R12" s="12" t="n">
+      <c r="R12" s="26" t="n">
         <v>-29.89</v>
       </c>
-      <c r="S12" s="12" t="n">
+      <c r="S12" s="26" t="n">
         <v>10.83</v>
       </c>
-      <c r="T12" s="12" t="n">
+      <c r="T12" s="26" t="n">
         <v>42.53</v>
       </c>
-      <c r="U12" s="12" t="n">
+      <c r="U12" s="26" t="n">
         <v>-6.95</v>
       </c>
-      <c r="V12" s="12" t="n">
+      <c r="V12" s="26" t="n">
         <v>-33.55</v>
       </c>
-      <c r="W12" s="12" t="n">
+      <c r="W12" s="26" t="n">
         <v>40.86</v>
       </c>
-      <c r="X12" s="12" t="n">
+      <c r="X12" s="26" t="n">
         <v>-4.23</v>
       </c>
-      <c r="Y12" s="12" t="n">
+      <c r="Y12" s="26" t="n">
         <v>-33.39</v>
       </c>
-      <c r="Z12" s="12" t="n">
+      <c r="Z12" s="26" t="n">
         <v>42.07</v>
       </c>
-      <c r="AA12" s="12" t="n">
+      <c r="AA12" s="26" t="n">
         <v>-5.18</v>
       </c>
-      <c r="AB12" s="12" t="n">
+      <c r="AB12" s="26" t="n">
         <v>-28.84</v>
       </c>
-      <c r="AC12" s="12" t="n">
+      <c r="AC12" s="26" t="n">
         <v>50.38</v>
       </c>
-      <c r="AD12" s="12" t="n">
+      <c r="AD12" s="26" t="n">
         <v>29.8</v>
       </c>
-      <c r="AE12" s="12" t="n">
+      <c r="AE12" s="26" t="n">
         <v>17.36</v>
       </c>
-      <c r="AF12" s="12" t="n">
+      <c r="AF12" s="26" t="n">
         <v>50.81</v>
       </c>
-      <c r="AG12" s="12" t="n">
+      <c r="AG12" s="26" t="n">
         <v>32.37</v>
       </c>
-      <c r="AH12" s="12" t="n">
+      <c r="AH12" s="26" t="n">
         <v>19.25</v>
       </c>
-      <c r="AI12" s="12" t="n">
+      <c r="AI12" s="26" t="n">
         <v>62.98</v>
       </c>
-      <c r="AJ12" s="12" t="n">
+      <c r="AJ12" s="26" t="n">
         <v>-29.39</v>
       </c>
-      <c r="AK12" s="12" t="n">
+      <c r="AK12" s="26" t="n">
         <v>12.93</v>
       </c>
-      <c r="AL12" s="12" t="n">
+      <c r="AL12" s="26" t="n">
         <v>63.17</v>
       </c>
-      <c r="AM12" s="12" t="n">
+      <c r="AM12" s="26" t="n">
         <v>-30.17</v>
       </c>
-      <c r="AN12" s="12" t="n">
+      <c r="AN12" s="26" t="n">
         <v>13.69</v>
       </c>
-      <c r="AO12" s="12" t="n">
+      <c r="AO12" s="26" t="n">
         <v>38.47</v>
       </c>
-      <c r="AP12" s="12" t="n">
+      <c r="AP12" s="26" t="n">
         <v>-5.18</v>
       </c>
-      <c r="AQ12" s="12" t="n">
+      <c r="AQ12" s="26" t="n">
         <v>-28.45</v>
       </c>
-      <c r="AR12" s="12" t="n">
+      <c r="AR12" s="26" t="n">
         <v>40.72</v>
       </c>
-      <c r="AS12" s="12" t="n">
+      <c r="AS12" s="26" t="n">
         <v>-6.72</v>
       </c>
-      <c r="AT12" s="12" t="n">
+      <c r="AT12" s="26" t="n">
         <v>-29.82</v>
       </c>
     </row>

--- a/experiments/敦煌变化数据_predicted.xlsx
+++ b/experiments/敦煌变化数据_predicted.xlsx
@@ -77,7 +77,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -112,6 +112,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F3E5F5"/>
         <bgColor rgb="00F3E5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E1BEE7"/>
+        <bgColor rgb="00E1BEE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -188,7 +194,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -262,6 +268,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -10576,59 +10585,59 @@
       <c r="J5" s="26" t="n">
         <v>17.6</v>
       </c>
-      <c r="K5" s="26" t="n">
-        <v>58.69</v>
-      </c>
-      <c r="L5" s="26" t="n">
-        <v>-32.46</v>
-      </c>
-      <c r="M5" s="26" t="n">
-        <v>15.24</v>
-      </c>
-      <c r="N5" s="26" t="n">
-        <v>57.49</v>
-      </c>
-      <c r="O5" s="26" t="n">
-        <v>-31.79</v>
-      </c>
-      <c r="P5" s="26" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="Q5" s="26" t="n">
-        <v>62.69</v>
-      </c>
-      <c r="R5" s="26" t="n">
-        <v>-32.05</v>
-      </c>
-      <c r="S5" s="26" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="T5" s="26" t="n">
-        <v>40.37</v>
-      </c>
-      <c r="U5" s="26" t="n">
-        <v>-5.07</v>
-      </c>
-      <c r="V5" s="26" t="n">
-        <v>-33.27</v>
-      </c>
-      <c r="W5" s="26" t="n">
-        <v>40.18</v>
-      </c>
-      <c r="X5" s="26" t="n">
-        <v>-6.11</v>
-      </c>
-      <c r="Y5" s="26" t="n">
-        <v>-31.11</v>
-      </c>
-      <c r="Z5" s="26" t="n">
-        <v>40.96</v>
-      </c>
-      <c r="AA5" s="26" t="n">
-        <v>-5.21</v>
-      </c>
-      <c r="AB5" s="26" t="n">
-        <v>-33.07</v>
+      <c r="K5" s="27" t="n">
+        <v>59.11</v>
+      </c>
+      <c r="L5" s="27" t="n">
+        <v>-32.14</v>
+      </c>
+      <c r="M5" s="27" t="n">
+        <v>15.47</v>
+      </c>
+      <c r="N5" s="27" t="n">
+        <v>58.16</v>
+      </c>
+      <c r="O5" s="27" t="n">
+        <v>-32.2</v>
+      </c>
+      <c r="P5" s="27" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="Q5" s="27" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="R5" s="27" t="n">
+        <v>-32.28</v>
+      </c>
+      <c r="S5" s="27" t="n">
+        <v>13.16</v>
+      </c>
+      <c r="T5" s="27" t="n">
+        <v>40.73</v>
+      </c>
+      <c r="U5" s="27" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="V5" s="27" t="n">
+        <v>-32.75</v>
+      </c>
+      <c r="W5" s="27" t="n">
+        <v>40.27</v>
+      </c>
+      <c r="X5" s="27" t="n">
+        <v>-5.63</v>
+      </c>
+      <c r="Y5" s="27" t="n">
+        <v>-31.91</v>
+      </c>
+      <c r="Z5" s="27" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="AA5" s="27" t="n">
+        <v>-5.25</v>
+      </c>
+      <c r="AB5" s="27" t="n">
+        <v>-32.94</v>
       </c>
       <c r="AC5" s="26" t="n">
         <v>47.69</v>
@@ -10648,41 +10657,41 @@
       <c r="AH5" s="26" t="n">
         <v>18.86</v>
       </c>
-      <c r="AI5" s="26" t="n">
-        <v>61.53</v>
-      </c>
-      <c r="AJ5" s="26" t="n">
-        <v>-30.89</v>
-      </c>
-      <c r="AK5" s="26" t="n">
-        <v>15.43</v>
-      </c>
-      <c r="AL5" s="26" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="AM5" s="26" t="n">
-        <v>-30.91</v>
-      </c>
-      <c r="AN5" s="26" t="n">
-        <v>14.18</v>
-      </c>
-      <c r="AO5" s="26" t="n">
-        <v>37.81</v>
-      </c>
-      <c r="AP5" s="26" t="n">
-        <v>-7.22</v>
-      </c>
-      <c r="AQ5" s="26" t="n">
-        <v>-28.06</v>
-      </c>
-      <c r="AR5" s="26" t="n">
-        <v>39.08</v>
-      </c>
-      <c r="AS5" s="26" t="n">
-        <v>-7.15</v>
-      </c>
-      <c r="AT5" s="26" t="n">
-        <v>-27.36</v>
+      <c r="AI5" s="27" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="AJ5" s="27" t="n">
+        <v>-31.25</v>
+      </c>
+      <c r="AK5" s="27" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="AL5" s="27" t="n">
+        <v>62.72</v>
+      </c>
+      <c r="AM5" s="27" t="n">
+        <v>-30.77</v>
+      </c>
+      <c r="AN5" s="27" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="AO5" s="27" t="n">
+        <v>38.59</v>
+      </c>
+      <c r="AP5" s="27" t="n">
+        <v>-6.23</v>
+      </c>
+      <c r="AQ5" s="27" t="n">
+        <v>-28.29</v>
+      </c>
+      <c r="AR5" s="27" t="n">
+        <v>39.19</v>
+      </c>
+      <c r="AS5" s="27" t="n">
+        <v>-7.2</v>
+      </c>
+      <c r="AT5" s="27" t="n">
+        <v>-27.58</v>
       </c>
     </row>
     <row r="6">
@@ -10718,59 +10727,59 @@
       <c r="J6" s="26" t="n">
         <v>16.93</v>
       </c>
-      <c r="K6" s="26" t="n">
-        <v>59.23</v>
-      </c>
-      <c r="L6" s="26" t="n">
-        <v>-31.9</v>
-      </c>
-      <c r="M6" s="26" t="n">
-        <v>16.16</v>
-      </c>
-      <c r="N6" s="26" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="O6" s="26" t="n">
-        <v>-32.83</v>
-      </c>
-      <c r="P6" s="26" t="n">
-        <v>16.34</v>
-      </c>
-      <c r="Q6" s="26" t="n">
-        <v>60.62</v>
-      </c>
-      <c r="R6" s="26" t="n">
-        <v>-32.96</v>
-      </c>
-      <c r="S6" s="26" t="n">
-        <v>15.41</v>
-      </c>
-      <c r="T6" s="26" t="n">
-        <v>40.79</v>
-      </c>
-      <c r="U6" s="26" t="n">
-        <v>-5.98</v>
-      </c>
-      <c r="V6" s="26" t="n">
-        <v>-31.71</v>
-      </c>
-      <c r="W6" s="26" t="n">
-        <v>40.23</v>
-      </c>
-      <c r="X6" s="26" t="n">
-        <v>-5.38</v>
-      </c>
-      <c r="Y6" s="26" t="n">
-        <v>-32.33</v>
-      </c>
-      <c r="Z6" s="26" t="n">
-        <v>40.17</v>
-      </c>
-      <c r="AA6" s="26" t="n">
-        <v>-5.16</v>
-      </c>
-      <c r="AB6" s="26" t="n">
-        <v>-33.39</v>
+      <c r="K6" s="27" t="n">
+        <v>58.95</v>
+      </c>
+      <c r="L6" s="27" t="n">
+        <v>-31.72</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="N6" s="27" t="n">
+        <v>57.96</v>
+      </c>
+      <c r="O6" s="27" t="n">
+        <v>-32.66</v>
+      </c>
+      <c r="P6" s="27" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="Q6" s="27" t="n">
+        <v>61.17</v>
+      </c>
+      <c r="R6" s="27" t="n">
+        <v>-32.24</v>
+      </c>
+      <c r="S6" s="27" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="T6" s="27" t="n">
+        <v>40.21</v>
+      </c>
+      <c r="U6" s="27" t="n">
+        <v>-5.44</v>
+      </c>
+      <c r="V6" s="27" t="n">
+        <v>-32.61</v>
+      </c>
+      <c r="W6" s="27" t="n">
+        <v>40.22</v>
+      </c>
+      <c r="X6" s="27" t="n">
+        <v>-5.58</v>
+      </c>
+      <c r="Y6" s="27" t="n">
+        <v>-31.99</v>
+      </c>
+      <c r="Z6" s="27" t="n">
+        <v>40.48</v>
+      </c>
+      <c r="AA6" s="27" t="n">
+        <v>-5.28</v>
+      </c>
+      <c r="AB6" s="27" t="n">
+        <v>-33.22</v>
       </c>
       <c r="AC6" s="26" t="n">
         <v>48.66</v>
@@ -10790,41 +10799,41 @@
       <c r="AH6" s="26" t="n">
         <v>18.97</v>
       </c>
-      <c r="AI6" s="26" t="n">
-        <v>60.23</v>
-      </c>
-      <c r="AJ6" s="26" t="n">
-        <v>-31.05</v>
-      </c>
-      <c r="AK6" s="26" t="n">
-        <v>14.58</v>
-      </c>
-      <c r="AL6" s="26" t="n">
-        <v>62.65</v>
-      </c>
-      <c r="AM6" s="26" t="n">
-        <v>-30.8</v>
-      </c>
-      <c r="AN6" s="26" t="n">
-        <v>14.14</v>
-      </c>
-      <c r="AO6" s="26" t="n">
-        <v>37.57</v>
-      </c>
-      <c r="AP6" s="26" t="n">
-        <v>-6.38</v>
-      </c>
-      <c r="AQ6" s="26" t="n">
-        <v>-28.08</v>
-      </c>
-      <c r="AR6" s="26" t="n">
-        <v>39.52</v>
-      </c>
-      <c r="AS6" s="26" t="n">
-        <v>-8.44</v>
-      </c>
-      <c r="AT6" s="26" t="n">
-        <v>-27.36</v>
+      <c r="AI6" s="27" t="n">
+        <v>60.81</v>
+      </c>
+      <c r="AJ6" s="27" t="n">
+        <v>-30.92</v>
+      </c>
+      <c r="AK6" s="27" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="AL6" s="27" t="n">
+        <v>62.66</v>
+      </c>
+      <c r="AM6" s="27" t="n">
+        <v>-30.83</v>
+      </c>
+      <c r="AN6" s="27" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="AO6" s="27" t="n">
+        <v>38.19</v>
+      </c>
+      <c r="AP6" s="27" t="n">
+        <v>-6.51</v>
+      </c>
+      <c r="AQ6" s="27" t="n">
+        <v>-27.75</v>
+      </c>
+      <c r="AR6" s="27" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="AS6" s="27" t="n">
+        <v>-7.68</v>
+      </c>
+      <c r="AT6" s="27" t="n">
+        <v>-27.69</v>
       </c>
     </row>
     <row r="7">
@@ -10860,59 +10869,59 @@
       <c r="J7" s="26" t="n">
         <v>15.47</v>
       </c>
-      <c r="K7" s="26" t="n">
-        <v>58.65</v>
-      </c>
-      <c r="L7" s="26" t="n">
-        <v>-30.63</v>
-      </c>
-      <c r="M7" s="26" t="n">
-        <v>14.77</v>
-      </c>
-      <c r="N7" s="26" t="n">
-        <v>57.58</v>
-      </c>
-      <c r="O7" s="26" t="n">
-        <v>-33.2</v>
-      </c>
-      <c r="P7" s="26" t="n">
-        <v>16.79</v>
-      </c>
-      <c r="Q7" s="26" t="n">
-        <v>60.76</v>
-      </c>
-      <c r="R7" s="26" t="n">
-        <v>-31.01</v>
-      </c>
-      <c r="S7" s="26" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="T7" s="26" t="n">
-        <v>38.89</v>
-      </c>
-      <c r="U7" s="26" t="n">
-        <v>-4.71</v>
-      </c>
-      <c r="V7" s="26" t="n">
-        <v>-33.74</v>
-      </c>
-      <c r="W7" s="26" t="n">
-        <v>40.23</v>
-      </c>
-      <c r="X7" s="26" t="n">
-        <v>-5.44</v>
-      </c>
-      <c r="Y7" s="26" t="n">
-        <v>-32.2</v>
-      </c>
-      <c r="Z7" s="26" t="n">
-        <v>40.64</v>
-      </c>
-      <c r="AA7" s="26" t="n">
-        <v>-5.58</v>
-      </c>
-      <c r="AB7" s="26" t="n">
-        <v>-33.04</v>
+      <c r="K7" s="27" t="n">
+        <v>59.05</v>
+      </c>
+      <c r="L7" s="27" t="n">
+        <v>-31.03</v>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="N7" s="27" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="O7" s="27" t="n">
+        <v>-32.9</v>
+      </c>
+      <c r="P7" s="27" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="Q7" s="27" t="n">
+        <v>59.96</v>
+      </c>
+      <c r="R7" s="27" t="n">
+        <v>-31.72</v>
+      </c>
+      <c r="S7" s="27" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="T7" s="27" t="n">
+        <v>40.41</v>
+      </c>
+      <c r="U7" s="27" t="n">
+        <v>-5.25</v>
+      </c>
+      <c r="V7" s="27" t="n">
+        <v>-32.19</v>
+      </c>
+      <c r="W7" s="27" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="X7" s="27" t="n">
+        <v>-5.22</v>
+      </c>
+      <c r="Y7" s="27" t="n">
+        <v>-32.48</v>
+      </c>
+      <c r="Z7" s="27" t="n">
+        <v>40.87</v>
+      </c>
+      <c r="AA7" s="27" t="n">
+        <v>-5.15</v>
+      </c>
+      <c r="AB7" s="27" t="n">
+        <v>-33.19</v>
       </c>
       <c r="AC7" s="26" t="n">
         <v>47.74</v>
@@ -10932,41 +10941,41 @@
       <c r="AH7" s="26" t="n">
         <v>18.25</v>
       </c>
-      <c r="AI7" s="26" t="n">
-        <v>61.24</v>
-      </c>
-      <c r="AJ7" s="26" t="n">
-        <v>-30.68</v>
-      </c>
-      <c r="AK7" s="26" t="n">
-        <v>15.19</v>
-      </c>
-      <c r="AL7" s="26" t="n">
-        <v>62.63</v>
-      </c>
-      <c r="AM7" s="26" t="n">
-        <v>-30.8</v>
-      </c>
-      <c r="AN7" s="26" t="n">
-        <v>14.54</v>
-      </c>
-      <c r="AO7" s="26" t="n">
-        <v>39.81</v>
-      </c>
-      <c r="AP7" s="26" t="n">
-        <v>-6.07</v>
-      </c>
-      <c r="AQ7" s="26" t="n">
-        <v>-26.79</v>
-      </c>
-      <c r="AR7" s="26" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="AS7" s="26" t="n">
-        <v>-6.68</v>
-      </c>
-      <c r="AT7" s="26" t="n">
-        <v>-28.69</v>
+      <c r="AI7" s="27" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="AJ7" s="27" t="n">
+        <v>-30.74</v>
+      </c>
+      <c r="AK7" s="27" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="AL7" s="27" t="n">
+        <v>62.62</v>
+      </c>
+      <c r="AM7" s="27" t="n">
+        <v>-30.87</v>
+      </c>
+      <c r="AN7" s="27" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="AO7" s="27" t="n">
+        <v>39.69</v>
+      </c>
+      <c r="AP7" s="27" t="n">
+        <v>-6.76</v>
+      </c>
+      <c r="AQ7" s="27" t="n">
+        <v>-26.33</v>
+      </c>
+      <c r="AR7" s="27" t="n">
+        <v>36.68</v>
+      </c>
+      <c r="AS7" s="27" t="n">
+        <v>-7.09</v>
+      </c>
+      <c r="AT7" s="27" t="n">
+        <v>-28.78</v>
       </c>
     </row>
     <row r="8">
@@ -11002,59 +11011,59 @@
       <c r="J8" s="26" t="n">
         <v>14.36</v>
       </c>
-      <c r="K8" s="26" t="n">
-        <v>59.66</v>
-      </c>
-      <c r="L8" s="26" t="n">
-        <v>-30.96</v>
-      </c>
-      <c r="M8" s="26" t="n">
-        <v>15</v>
-      </c>
-      <c r="N8" s="26" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="O8" s="26" t="n">
-        <v>-32.36</v>
-      </c>
-      <c r="P8" s="26" t="n">
-        <v>15.52</v>
-      </c>
-      <c r="Q8" s="26" t="n">
-        <v>57.69</v>
-      </c>
-      <c r="R8" s="26" t="n">
-        <v>-31.89</v>
-      </c>
-      <c r="S8" s="26" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="T8" s="26" t="n">
-        <v>43.07</v>
-      </c>
-      <c r="U8" s="26" t="n">
-        <v>-5.61</v>
-      </c>
-      <c r="V8" s="26" t="n">
-        <v>-29.58</v>
-      </c>
-      <c r="W8" s="26" t="n">
-        <v>41.01</v>
-      </c>
-      <c r="X8" s="26" t="n">
-        <v>-4.63</v>
-      </c>
-      <c r="Y8" s="26" t="n">
-        <v>-33.2</v>
-      </c>
-      <c r="Z8" s="26" t="n">
-        <v>42.04</v>
-      </c>
-      <c r="AA8" s="26" t="n">
-        <v>-4.29</v>
-      </c>
-      <c r="AB8" s="26" t="n">
-        <v>-33.3</v>
+      <c r="K8" s="27" t="n">
+        <v>59.45</v>
+      </c>
+      <c r="L8" s="27" t="n">
+        <v>-31.11</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="N8" s="27" t="n">
+        <v>57.84</v>
+      </c>
+      <c r="O8" s="27" t="n">
+        <v>-32.73</v>
+      </c>
+      <c r="P8" s="27" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="Q8" s="27" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="R8" s="27" t="n">
+        <v>-30.73</v>
+      </c>
+      <c r="S8" s="27" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="T8" s="27" t="n">
+        <v>41.58</v>
+      </c>
+      <c r="U8" s="27" t="n">
+        <v>-5.39</v>
+      </c>
+      <c r="V8" s="27" t="n">
+        <v>-31.39</v>
+      </c>
+      <c r="W8" s="27" t="n">
+        <v>40.88</v>
+      </c>
+      <c r="X8" s="27" t="n">
+        <v>-5.12</v>
+      </c>
+      <c r="Y8" s="27" t="n">
+        <v>-32.63</v>
+      </c>
+      <c r="Z8" s="27" t="n">
+        <v>41.49</v>
+      </c>
+      <c r="AA8" s="27" t="n">
+        <v>-4.48</v>
+      </c>
+      <c r="AB8" s="27" t="n">
+        <v>-33.64</v>
       </c>
       <c r="AC8" s="26" t="n">
         <v>49.39</v>
@@ -11074,41 +11083,41 @@
       <c r="AH8" s="26" t="n">
         <v>17.4</v>
       </c>
-      <c r="AI8" s="26" t="n">
-        <v>62.87</v>
-      </c>
-      <c r="AJ8" s="26" t="n">
-        <v>-30.56</v>
-      </c>
-      <c r="AK8" s="26" t="n">
-        <v>14.46</v>
-      </c>
-      <c r="AL8" s="26" t="n">
-        <v>62.56</v>
-      </c>
-      <c r="AM8" s="26" t="n">
-        <v>-31.08</v>
-      </c>
-      <c r="AN8" s="26" t="n">
-        <v>14.58</v>
-      </c>
-      <c r="AO8" s="26" t="n">
-        <v>41.57</v>
-      </c>
-      <c r="AP8" s="26" t="n">
-        <v>-8.51</v>
-      </c>
-      <c r="AQ8" s="26" t="n">
-        <v>-23.67</v>
-      </c>
-      <c r="AR8" s="26" t="n">
-        <v>33</v>
-      </c>
-      <c r="AS8" s="26" t="n">
-        <v>-6.58</v>
-      </c>
-      <c r="AT8" s="26" t="n">
-        <v>-30.37</v>
+      <c r="AI8" s="27" t="n">
+        <v>62.35</v>
+      </c>
+      <c r="AJ8" s="27" t="n">
+        <v>-30.21</v>
+      </c>
+      <c r="AK8" s="27" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="AL8" s="27" t="n">
+        <v>62.69</v>
+      </c>
+      <c r="AM8" s="27" t="n">
+        <v>-30.78</v>
+      </c>
+      <c r="AN8" s="27" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="AO8" s="27" t="n">
+        <v>40.34</v>
+      </c>
+      <c r="AP8" s="27" t="n">
+        <v>-7.53</v>
+      </c>
+      <c r="AQ8" s="27" t="n">
+        <v>-25.43</v>
+      </c>
+      <c r="AR8" s="27" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="AS8" s="27" t="n">
+        <v>-6.69</v>
+      </c>
+      <c r="AT8" s="27" t="n">
+        <v>-29.74</v>
       </c>
     </row>
     <row r="9">
@@ -11144,59 +11153,59 @@
       <c r="J9" s="26" t="n">
         <v>15.21</v>
       </c>
-      <c r="K9" s="26" t="n">
-        <v>59.84</v>
-      </c>
-      <c r="L9" s="26" t="n">
-        <v>-31.9</v>
-      </c>
-      <c r="M9" s="26" t="n">
-        <v>15.31</v>
-      </c>
-      <c r="N9" s="26" t="n">
-        <v>58.38</v>
-      </c>
-      <c r="O9" s="26" t="n">
-        <v>-32.99</v>
-      </c>
-      <c r="P9" s="26" t="n">
-        <v>16.66</v>
-      </c>
-      <c r="Q9" s="26" t="n">
-        <v>62.27</v>
-      </c>
-      <c r="R9" s="26" t="n">
-        <v>-28.15</v>
-      </c>
-      <c r="S9" s="26" t="n">
-        <v>18.47</v>
-      </c>
-      <c r="T9" s="26" t="n">
-        <v>41.28</v>
-      </c>
-      <c r="U9" s="26" t="n">
-        <v>-5.65</v>
-      </c>
-      <c r="V9" s="26" t="n">
-        <v>-32.66</v>
-      </c>
-      <c r="W9" s="26" t="n">
-        <v>41.28</v>
-      </c>
-      <c r="X9" s="26" t="n">
-        <v>-5.79</v>
-      </c>
-      <c r="Y9" s="26" t="n">
-        <v>-31.93</v>
-      </c>
-      <c r="Z9" s="26" t="n">
-        <v>41.25</v>
-      </c>
-      <c r="AA9" s="26" t="n">
-        <v>-3.77</v>
-      </c>
-      <c r="AB9" s="26" t="n">
-        <v>-34.92</v>
+      <c r="K9" s="27" t="n">
+        <v>60.08</v>
+      </c>
+      <c r="L9" s="27" t="n">
+        <v>-31.51</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="N9" s="27" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="O9" s="27" t="n">
+        <v>-32.68</v>
+      </c>
+      <c r="P9" s="27" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="Q9" s="27" t="n">
+        <v>61.01</v>
+      </c>
+      <c r="R9" s="27" t="n">
+        <v>-29.28</v>
+      </c>
+      <c r="S9" s="27" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="T9" s="27" t="n">
+        <v>42.67</v>
+      </c>
+      <c r="U9" s="27" t="n">
+        <v>-5.87</v>
+      </c>
+      <c r="V9" s="27" t="n">
+        <v>-30.53</v>
+      </c>
+      <c r="W9" s="27" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="X9" s="27" t="n">
+        <v>-5.15</v>
+      </c>
+      <c r="Y9" s="27" t="n">
+        <v>-32.73</v>
+      </c>
+      <c r="Z9" s="27" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="AA9" s="27" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="AB9" s="27" t="n">
+        <v>-34.44</v>
       </c>
       <c r="AC9" s="26" t="n">
         <v>49.91</v>
@@ -11216,41 +11225,41 @@
       <c r="AH9" s="26" t="n">
         <v>18.46</v>
       </c>
-      <c r="AI9" s="26" t="n">
-        <v>62.44</v>
-      </c>
-      <c r="AJ9" s="26" t="n">
-        <v>-29.06</v>
-      </c>
-      <c r="AK9" s="26" t="n">
-        <v>11.93</v>
-      </c>
-      <c r="AL9" s="26" t="n">
-        <v>63</v>
-      </c>
-      <c r="AM9" s="26" t="n">
-        <v>-30.16</v>
-      </c>
-      <c r="AN9" s="26" t="n">
-        <v>13.85</v>
-      </c>
-      <c r="AO9" s="26" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="AP9" s="26" t="n">
-        <v>-7.03</v>
-      </c>
-      <c r="AQ9" s="26" t="n">
-        <v>-27.61</v>
-      </c>
-      <c r="AR9" s="26" t="n">
-        <v>39.97</v>
-      </c>
-      <c r="AS9" s="26" t="n">
-        <v>-6.93</v>
-      </c>
-      <c r="AT9" s="26" t="n">
-        <v>-29.54</v>
+      <c r="AI9" s="27" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="AJ9" s="27" t="n">
+        <v>-29.27</v>
+      </c>
+      <c r="AK9" s="27" t="n">
+        <v>12.38</v>
+      </c>
+      <c r="AL9" s="27" t="n">
+        <v>62.89</v>
+      </c>
+      <c r="AM9" s="27" t="n">
+        <v>-30.53</v>
+      </c>
+      <c r="AN9" s="27" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="AO9" s="27" t="n">
+        <v>40.13</v>
+      </c>
+      <c r="AP9" s="27" t="n">
+        <v>-7.58</v>
+      </c>
+      <c r="AQ9" s="27" t="n">
+        <v>-25.68</v>
+      </c>
+      <c r="AR9" s="27" t="n">
+        <v>38.33</v>
+      </c>
+      <c r="AS9" s="27" t="n">
+        <v>-6.97</v>
+      </c>
+      <c r="AT9" s="27" t="n">
+        <v>-29.5</v>
       </c>
     </row>
     <row r="10">
@@ -11286,59 +11295,59 @@
       <c r="J10" s="26" t="n">
         <v>15.31</v>
       </c>
-      <c r="K10" s="26" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="L10" s="26" t="n">
-        <v>-31.29</v>
-      </c>
-      <c r="M10" s="26" t="n">
-        <v>13.48</v>
-      </c>
-      <c r="N10" s="26" t="n">
-        <v>58.28</v>
-      </c>
-      <c r="O10" s="26" t="n">
-        <v>-32.38</v>
-      </c>
-      <c r="P10" s="26" t="n">
-        <v>15.98</v>
-      </c>
-      <c r="Q10" s="26" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="R10" s="26" t="n">
-        <v>-28.93</v>
-      </c>
-      <c r="S10" s="26" t="n">
-        <v>12.32</v>
-      </c>
-      <c r="T10" s="26" t="n">
-        <v>45.04</v>
-      </c>
-      <c r="U10" s="26" t="n">
-        <v>-6.57</v>
-      </c>
-      <c r="V10" s="26" t="n">
-        <v>-27.23</v>
-      </c>
-      <c r="W10" s="26" t="n">
-        <v>41.24</v>
-      </c>
-      <c r="X10" s="26" t="n">
-        <v>-4.37</v>
-      </c>
-      <c r="Y10" s="26" t="n">
-        <v>-33.88</v>
-      </c>
-      <c r="Z10" s="26" t="n">
-        <v>41.06</v>
-      </c>
-      <c r="AA10" s="26" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AB10" s="26" t="n">
-        <v>-34.61</v>
+      <c r="K10" s="27" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="L10" s="27" t="n">
+        <v>-31.41</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>14.64</v>
+      </c>
+      <c r="N10" s="27" t="n">
+        <v>58.41</v>
+      </c>
+      <c r="O10" s="27" t="n">
+        <v>-32.36</v>
+      </c>
+      <c r="P10" s="27" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="Q10" s="27" t="n">
+        <v>61.58</v>
+      </c>
+      <c r="R10" s="27" t="n">
+        <v>-28.83</v>
+      </c>
+      <c r="S10" s="27" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="T10" s="27" t="n">
+        <v>44.51</v>
+      </c>
+      <c r="U10" s="27" t="n">
+        <v>-6.68</v>
+      </c>
+      <c r="V10" s="27" t="n">
+        <v>-29.48</v>
+      </c>
+      <c r="W10" s="27" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="X10" s="27" t="n">
+        <v>-4.69</v>
+      </c>
+      <c r="Y10" s="27" t="n">
+        <v>-33.56</v>
+      </c>
+      <c r="Z10" s="27" t="n">
+        <v>41.35</v>
+      </c>
+      <c r="AA10" s="27" t="n">
+        <v>-4.9</v>
+      </c>
+      <c r="AB10" s="27" t="n">
+        <v>-33.95</v>
       </c>
       <c r="AC10" s="26" t="n">
         <v>50.18</v>
@@ -11358,41 +11367,41 @@
       <c r="AH10" s="26" t="n">
         <v>18.15</v>
       </c>
-      <c r="AI10" s="26" t="n">
-        <v>59.51</v>
-      </c>
-      <c r="AJ10" s="26" t="n">
-        <v>-28.4</v>
-      </c>
-      <c r="AK10" s="26" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="AL10" s="26" t="n">
-        <v>63</v>
-      </c>
-      <c r="AM10" s="26" t="n">
-        <v>-30.7</v>
-      </c>
-      <c r="AN10" s="26" t="n">
-        <v>15.52</v>
-      </c>
-      <c r="AO10" s="26" t="n">
-        <v>42.15</v>
-      </c>
-      <c r="AP10" s="26" t="n">
-        <v>-7.76</v>
-      </c>
-      <c r="AQ10" s="26" t="n">
-        <v>-23.81</v>
-      </c>
-      <c r="AR10" s="26" t="n">
-        <v>40.39</v>
-      </c>
-      <c r="AS10" s="26" t="n">
-        <v>-7.45</v>
-      </c>
-      <c r="AT10" s="26" t="n">
-        <v>-28.56</v>
+      <c r="AI10" s="27" t="n">
+        <v>60.93</v>
+      </c>
+      <c r="AJ10" s="27" t="n">
+        <v>-28.41</v>
+      </c>
+      <c r="AK10" s="27" t="n">
+        <v>11.43</v>
+      </c>
+      <c r="AL10" s="27" t="n">
+        <v>62.95</v>
+      </c>
+      <c r="AM10" s="27" t="n">
+        <v>-30.48</v>
+      </c>
+      <c r="AN10" s="27" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="AO10" s="27" t="n">
+        <v>40.66</v>
+      </c>
+      <c r="AP10" s="27" t="n">
+        <v>-7.48</v>
+      </c>
+      <c r="AQ10" s="27" t="n">
+        <v>-25.49</v>
+      </c>
+      <c r="AR10" s="27" t="n">
+        <v>40.28</v>
+      </c>
+      <c r="AS10" s="27" t="n">
+        <v>-7.52</v>
+      </c>
+      <c r="AT10" s="27" t="n">
+        <v>-28.47</v>
       </c>
     </row>
     <row r="11">
@@ -11428,59 +11437,59 @@
       <c r="J11" s="26" t="n">
         <v>14.81</v>
       </c>
-      <c r="K11" s="26" t="n">
-        <v>61.21</v>
-      </c>
-      <c r="L11" s="26" t="n">
-        <v>-31.17</v>
-      </c>
-      <c r="M11" s="26" t="n">
-        <v>16.27</v>
-      </c>
-      <c r="N11" s="26" t="n">
-        <v>58.68</v>
-      </c>
-      <c r="O11" s="26" t="n">
+      <c r="K11" s="27" t="n">
+        <v>60.94</v>
+      </c>
+      <c r="L11" s="27" t="n">
+        <v>-31.38</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>15.31</v>
+      </c>
+      <c r="N11" s="27" t="n">
+        <v>58.23</v>
+      </c>
+      <c r="O11" s="27" t="n">
+        <v>-31.76</v>
+      </c>
+      <c r="P11" s="27" t="n">
+        <v>16.69</v>
+      </c>
+      <c r="Q11" s="27" t="n">
+        <v>60.53</v>
+      </c>
+      <c r="R11" s="27" t="n">
+        <v>-29.37</v>
+      </c>
+      <c r="S11" s="27" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="T11" s="27" t="n">
+        <v>45.24</v>
+      </c>
+      <c r="U11" s="27" t="n">
+        <v>-7.35</v>
+      </c>
+      <c r="V11" s="27" t="n">
+        <v>-30.59</v>
+      </c>
+      <c r="W11" s="27" t="n">
+        <v>40.88</v>
+      </c>
+      <c r="X11" s="27" t="n">
+        <v>-4.27</v>
+      </c>
+      <c r="Y11" s="27" t="n">
+        <v>-34.09</v>
+      </c>
+      <c r="Z11" s="27" t="n">
+        <v>41.79</v>
+      </c>
+      <c r="AA11" s="27" t="n">
+        <v>-5.46</v>
+      </c>
+      <c r="AB11" s="27" t="n">
         <v>-31.7</v>
-      </c>
-      <c r="P11" s="26" t="n">
-        <v>17.13</v>
-      </c>
-      <c r="Q11" s="26" t="n">
-        <v>60.44</v>
-      </c>
-      <c r="R11" s="26" t="n">
-        <v>-29.33</v>
-      </c>
-      <c r="S11" s="26" t="n">
-        <v>15.02</v>
-      </c>
-      <c r="T11" s="26" t="n">
-        <v>46.69</v>
-      </c>
-      <c r="U11" s="26" t="n">
-        <v>-7.95</v>
-      </c>
-      <c r="V11" s="26" t="n">
-        <v>-30.8</v>
-      </c>
-      <c r="W11" s="26" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="X11" s="26" t="n">
-        <v>-4.24</v>
-      </c>
-      <c r="Y11" s="26" t="n">
-        <v>-34.54</v>
-      </c>
-      <c r="Z11" s="26" t="n">
-        <v>42.02</v>
-      </c>
-      <c r="AA11" s="26" t="n">
-        <v>-5.82</v>
-      </c>
-      <c r="AB11" s="26" t="n">
-        <v>-31.68</v>
       </c>
       <c r="AC11" s="26" t="n">
         <v>50.44</v>
@@ -11500,41 +11509,41 @@
       <c r="AH11" s="26" t="n">
         <v>18.73</v>
       </c>
-      <c r="AI11" s="26" t="n">
-        <v>62.26</v>
-      </c>
-      <c r="AJ11" s="26" t="n">
-        <v>-27.76</v>
-      </c>
-      <c r="AK11" s="26" t="n">
-        <v>11.41</v>
-      </c>
-      <c r="AL11" s="26" t="n">
-        <v>62.82</v>
-      </c>
-      <c r="AM11" s="26" t="n">
-        <v>-30.38</v>
-      </c>
-      <c r="AN11" s="26" t="n">
-        <v>14.09</v>
-      </c>
-      <c r="AO11" s="26" t="n">
-        <v>39.92</v>
-      </c>
-      <c r="AP11" s="26" t="n">
-        <v>-7.36</v>
-      </c>
-      <c r="AQ11" s="26" t="n">
-        <v>-26.72</v>
-      </c>
-      <c r="AR11" s="26" t="n">
-        <v>40.39</v>
-      </c>
-      <c r="AS11" s="26" t="n">
-        <v>-8.27</v>
-      </c>
-      <c r="AT11" s="26" t="n">
-        <v>-27.21</v>
+      <c r="AI11" s="27" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="AJ11" s="27" t="n">
+        <v>-28.33</v>
+      </c>
+      <c r="AK11" s="27" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="AL11" s="27" t="n">
+        <v>62.95</v>
+      </c>
+      <c r="AM11" s="27" t="n">
+        <v>-30.41</v>
+      </c>
+      <c r="AN11" s="27" t="n">
+        <v>14.35</v>
+      </c>
+      <c r="AO11" s="27" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="AP11" s="27" t="n">
+        <v>-6.92</v>
+      </c>
+      <c r="AQ11" s="27" t="n">
+        <v>-26.43</v>
+      </c>
+      <c r="AR11" s="27" t="n">
+        <v>40.47</v>
+      </c>
+      <c r="AS11" s="27" t="n">
+        <v>-7.68</v>
+      </c>
+      <c r="AT11" s="27" t="n">
+        <v>-28.2</v>
       </c>
     </row>
     <row r="12">

--- a/experiments/敦煌变化数据_predicted.xlsx
+++ b/experiments/敦煌变化数据_predicted.xlsx
@@ -10558,32 +10558,32 @@
           <t>4.20</t>
         </is>
       </c>
-      <c r="B5" s="26" t="n">
-        <v>45.67</v>
-      </c>
-      <c r="C5" s="26" t="n">
-        <v>33.99</v>
-      </c>
-      <c r="D5" s="26" t="n">
+      <c r="B5" s="27" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="D5" s="27" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>36.52</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>16.78</v>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>48.06</v>
+      </c>
+      <c r="I5" s="27" t="n">
+        <v>34.56</v>
+      </c>
+      <c r="J5" s="27" t="n">
         <v>17.95</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>46.97</v>
-      </c>
-      <c r="F5" s="26" t="n">
-        <v>37.01</v>
-      </c>
-      <c r="G5" s="26" t="n">
-        <v>16.01</v>
-      </c>
-      <c r="H5" s="26" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I5" s="26" t="n">
-        <v>34.47</v>
-      </c>
-      <c r="J5" s="26" t="n">
-        <v>17.6</v>
       </c>
       <c r="K5" s="27" t="n">
         <v>59.11</v>
@@ -10639,23 +10639,23 @@
       <c r="AB5" s="27" t="n">
         <v>-32.94</v>
       </c>
-      <c r="AC5" s="26" t="n">
-        <v>47.69</v>
-      </c>
-      <c r="AD5" s="26" t="n">
-        <v>34.29</v>
-      </c>
-      <c r="AE5" s="26" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="AF5" s="26" t="n">
-        <v>49.49</v>
-      </c>
-      <c r="AG5" s="26" t="n">
-        <v>34.86</v>
-      </c>
-      <c r="AH5" s="26" t="n">
-        <v>18.86</v>
+      <c r="AC5" s="27" t="n">
+        <v>48.31</v>
+      </c>
+      <c r="AD5" s="27" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="AE5" s="27" t="n">
+        <v>20.37</v>
+      </c>
+      <c r="AF5" s="27" t="n">
+        <v>50.09</v>
+      </c>
+      <c r="AG5" s="27" t="n">
+        <v>34.77</v>
+      </c>
+      <c r="AH5" s="27" t="n">
+        <v>19.47</v>
       </c>
       <c r="AI5" s="27" t="n">
         <v>60.77</v>
@@ -10700,32 +10700,32 @@
           <t>4.23</t>
         </is>
       </c>
-      <c r="B6" s="26" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="C6" s="26" t="n">
-        <v>32.95</v>
-      </c>
-      <c r="D6" s="26" t="n">
-        <v>18.59</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>46.45</v>
-      </c>
-      <c r="F6" s="26" t="n">
-        <v>36.03</v>
-      </c>
-      <c r="G6" s="26" t="n">
-        <v>16.11</v>
-      </c>
-      <c r="H6" s="26" t="n">
-        <v>47.86</v>
-      </c>
-      <c r="I6" s="26" t="n">
-        <v>33.56</v>
-      </c>
-      <c r="J6" s="26" t="n">
-        <v>16.93</v>
+      <c r="B6" s="27" t="n">
+        <v>45.61</v>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>33.21</v>
+      </c>
+      <c r="D6" s="27" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>46.62</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>47.55</v>
+      </c>
+      <c r="I6" s="27" t="n">
+        <v>33.84</v>
+      </c>
+      <c r="J6" s="27" t="n">
+        <v>16.73</v>
       </c>
       <c r="K6" s="27" t="n">
         <v>58.95</v>
@@ -10781,23 +10781,23 @@
       <c r="AB6" s="27" t="n">
         <v>-33.22</v>
       </c>
-      <c r="AC6" s="26" t="n">
-        <v>48.66</v>
-      </c>
-      <c r="AD6" s="26" t="n">
-        <v>34.13</v>
-      </c>
-      <c r="AE6" s="26" t="n">
-        <v>21.01</v>
-      </c>
-      <c r="AF6" s="26" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="AG6" s="26" t="n">
-        <v>34.58</v>
-      </c>
-      <c r="AH6" s="26" t="n">
-        <v>18.97</v>
+      <c r="AC6" s="27" t="n">
+        <v>48.19</v>
+      </c>
+      <c r="AD6" s="27" t="n">
+        <v>34.33</v>
+      </c>
+      <c r="AE6" s="27" t="n">
+        <v>20.35</v>
+      </c>
+      <c r="AF6" s="27" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="AG6" s="27" t="n">
+        <v>34.09</v>
+      </c>
+      <c r="AH6" s="27" t="n">
+        <v>18.76</v>
       </c>
       <c r="AI6" s="27" t="n">
         <v>60.81</v>
@@ -10842,32 +10842,32 @@
           <t>4.26</t>
         </is>
       </c>
-      <c r="B7" s="26" t="n">
-        <v>45.55</v>
-      </c>
-      <c r="C7" s="26" t="n">
-        <v>32.93</v>
-      </c>
-      <c r="D7" s="26" t="n">
-        <v>18.05</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>46.62</v>
-      </c>
-      <c r="F7" s="26" t="n">
-        <v>37.39</v>
-      </c>
-      <c r="G7" s="26" t="n">
-        <v>16.42</v>
-      </c>
-      <c r="H7" s="26" t="n">
-        <v>46.38</v>
-      </c>
-      <c r="I7" s="26" t="n">
-        <v>33.79</v>
-      </c>
-      <c r="J7" s="26" t="n">
-        <v>15.47</v>
+      <c r="B7" s="27" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="D7" s="27" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="I7" s="27" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="J7" s="27" t="n">
+        <v>15.56</v>
       </c>
       <c r="K7" s="27" t="n">
         <v>59.05</v>
@@ -10923,23 +10923,23 @@
       <c r="AB7" s="27" t="n">
         <v>-33.19</v>
       </c>
-      <c r="AC7" s="26" t="n">
-        <v>47.74</v>
-      </c>
-      <c r="AD7" s="26" t="n">
-        <v>34.76</v>
-      </c>
-      <c r="AE7" s="26" t="n">
-        <v>20.28</v>
-      </c>
-      <c r="AF7" s="26" t="n">
-        <v>49.68</v>
-      </c>
-      <c r="AG7" s="26" t="n">
-        <v>32.32</v>
-      </c>
-      <c r="AH7" s="26" t="n">
-        <v>18.25</v>
+      <c r="AC7" s="27" t="n">
+        <v>48.38</v>
+      </c>
+      <c r="AD7" s="27" t="n">
+        <v>33.73</v>
+      </c>
+      <c r="AE7" s="27" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="AF7" s="27" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="AG7" s="27" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="AH7" s="27" t="n">
+        <v>18.22</v>
       </c>
       <c r="AI7" s="27" t="n">
         <v>61.4</v>
@@ -10984,32 +10984,32 @@
           <t>4.29</t>
         </is>
       </c>
-      <c r="B8" s="26" t="n">
-        <v>46.49</v>
-      </c>
-      <c r="C8" s="26" t="n">
-        <v>33.44</v>
-      </c>
-      <c r="D8" s="26" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>45.58</v>
-      </c>
-      <c r="F8" s="26" t="n">
-        <v>36.38</v>
-      </c>
-      <c r="G8" s="26" t="n">
-        <v>16.16</v>
-      </c>
-      <c r="H8" s="26" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="I8" s="26" t="n">
-        <v>33.67</v>
-      </c>
-      <c r="J8" s="26" t="n">
-        <v>14.36</v>
+      <c r="B8" s="27" t="n">
+        <v>46.26</v>
+      </c>
+      <c r="C8" s="27" t="n">
+        <v>33.48</v>
+      </c>
+      <c r="D8" s="27" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>45.79</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>36.21</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>46.67</v>
+      </c>
+      <c r="I8" s="27" t="n">
+        <v>33.75</v>
+      </c>
+      <c r="J8" s="27" t="n">
+        <v>14.85</v>
       </c>
       <c r="K8" s="27" t="n">
         <v>59.45</v>
@@ -11065,23 +11065,23 @@
       <c r="AB8" s="27" t="n">
         <v>-33.64</v>
       </c>
-      <c r="AC8" s="26" t="n">
-        <v>49.39</v>
-      </c>
-      <c r="AD8" s="26" t="n">
-        <v>31.28</v>
-      </c>
-      <c r="AE8" s="26" t="n">
-        <v>16.38</v>
-      </c>
-      <c r="AF8" s="26" t="n">
-        <v>50.58</v>
-      </c>
-      <c r="AG8" s="26" t="n">
-        <v>31.76</v>
-      </c>
-      <c r="AH8" s="26" t="n">
-        <v>17.4</v>
+      <c r="AC8" s="27" t="n">
+        <v>49.11</v>
+      </c>
+      <c r="AD8" s="27" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="AE8" s="27" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="AF8" s="27" t="n">
+        <v>50.45</v>
+      </c>
+      <c r="AG8" s="27" t="n">
+        <v>32.34</v>
+      </c>
+      <c r="AH8" s="27" t="n">
+        <v>17.88</v>
       </c>
       <c r="AI8" s="27" t="n">
         <v>62.35</v>
@@ -11126,32 +11126,32 @@
           <t>5.12</t>
         </is>
       </c>
-      <c r="B9" s="26" t="n">
-        <v>46.51</v>
-      </c>
-      <c r="C9" s="26" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="D9" s="26" t="n">
-        <v>16.28</v>
-      </c>
-      <c r="E9" s="26" t="n">
-        <v>45.39</v>
-      </c>
-      <c r="F9" s="26" t="n">
-        <v>34.69</v>
-      </c>
-      <c r="G9" s="26" t="n">
-        <v>16.02</v>
-      </c>
-      <c r="H9" s="26" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="I9" s="26" t="n">
-        <v>33.89</v>
-      </c>
-      <c r="J9" s="26" t="n">
-        <v>15.21</v>
+      <c r="B9" s="27" t="n">
+        <v>46.49</v>
+      </c>
+      <c r="C9" s="27" t="n">
+        <v>33.84</v>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>16.44</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>45.43</v>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>34.74</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="I9" s="27" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="J9" s="27" t="n">
+        <v>15.02</v>
       </c>
       <c r="K9" s="27" t="n">
         <v>60.08</v>
@@ -11207,23 +11207,23 @@
       <c r="AB9" s="27" t="n">
         <v>-34.44</v>
       </c>
-      <c r="AC9" s="26" t="n">
-        <v>49.91</v>
-      </c>
-      <c r="AD9" s="26" t="n">
-        <v>31.89</v>
-      </c>
-      <c r="AE9" s="26" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="AF9" s="26" t="n">
-        <v>50.95</v>
-      </c>
-      <c r="AG9" s="26" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="AH9" s="26" t="n">
-        <v>18.46</v>
+      <c r="AC9" s="27" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="AD9" s="27" t="n">
+        <v>31.07</v>
+      </c>
+      <c r="AE9" s="27" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="AF9" s="27" t="n">
+        <v>50.88</v>
+      </c>
+      <c r="AG9" s="27" t="n">
+        <v>33.06</v>
+      </c>
+      <c r="AH9" s="27" t="n">
+        <v>18.12</v>
       </c>
       <c r="AI9" s="27" t="n">
         <v>61.81</v>
@@ -11268,32 +11268,32 @@
           <t>5.14</t>
         </is>
       </c>
-      <c r="B10" s="26" t="n">
-        <v>46.47</v>
-      </c>
-      <c r="C10" s="26" t="n">
-        <v>33.71</v>
-      </c>
-      <c r="D10" s="26" t="n">
-        <v>16.36</v>
-      </c>
-      <c r="E10" s="26" t="n">
-        <v>45.37</v>
-      </c>
-      <c r="F10" s="26" t="n">
-        <v>33.19</v>
-      </c>
-      <c r="G10" s="26" t="n">
-        <v>15.36</v>
-      </c>
-      <c r="H10" s="26" t="n">
-        <v>47.27</v>
-      </c>
-      <c r="I10" s="26" t="n">
-        <v>33.51</v>
-      </c>
-      <c r="J10" s="26" t="n">
-        <v>15.31</v>
+      <c r="B10" s="27" t="n">
+        <v>46.52</v>
+      </c>
+      <c r="C10" s="27" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="D10" s="27" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>46.99</v>
+      </c>
+      <c r="I10" s="27" t="n">
+        <v>33.61</v>
+      </c>
+      <c r="J10" s="27" t="n">
+        <v>15.16</v>
       </c>
       <c r="K10" s="27" t="n">
         <v>60.75</v>
@@ -11352,20 +11352,20 @@
       <c r="AC10" s="26" t="n">
         <v>50.18</v>
       </c>
-      <c r="AD10" s="26" t="n">
-        <v>29.21</v>
-      </c>
-      <c r="AE10" s="26" t="n">
-        <v>16.05</v>
-      </c>
-      <c r="AF10" s="26" t="n">
-        <v>51.02</v>
-      </c>
-      <c r="AG10" s="26" t="n">
-        <v>33.43</v>
-      </c>
-      <c r="AH10" s="26" t="n">
-        <v>18.15</v>
+      <c r="AD10" s="27" t="n">
+        <v>29.88</v>
+      </c>
+      <c r="AE10" s="27" t="n">
+        <v>15.04</v>
+      </c>
+      <c r="AF10" s="27" t="n">
+        <v>50.87</v>
+      </c>
+      <c r="AG10" s="27" t="n">
+        <v>33.66</v>
+      </c>
+      <c r="AH10" s="27" t="n">
+        <v>18.37</v>
       </c>
       <c r="AI10" s="27" t="n">
         <v>60.93</v>
@@ -11410,32 +11410,32 @@
           <t>5.18</t>
         </is>
       </c>
-      <c r="B11" s="26" t="n">
-        <v>46.63</v>
-      </c>
-      <c r="C11" s="26" t="n">
-        <v>32.98</v>
-      </c>
-      <c r="D11" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="E11" s="26" t="n">
-        <v>44.29</v>
-      </c>
-      <c r="F11" s="26" t="n">
-        <v>34.07</v>
-      </c>
-      <c r="G11" s="26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="H11" s="26" t="n">
-        <v>46.73</v>
-      </c>
-      <c r="I11" s="26" t="n">
-        <v>33.55</v>
-      </c>
-      <c r="J11" s="26" t="n">
-        <v>14.81</v>
+      <c r="B11" s="27" t="n">
+        <v>46.54</v>
+      </c>
+      <c r="C11" s="27" t="n">
+        <v>33.13</v>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>16.04</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>15.27</v>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>46.86</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>33.49</v>
+      </c>
+      <c r="J11" s="27" t="n">
+        <v>14.93</v>
       </c>
       <c r="K11" s="27" t="n">
         <v>60.94</v>
@@ -11491,23 +11491,23 @@
       <c r="AB11" s="27" t="n">
         <v>-31.7</v>
       </c>
-      <c r="AC11" s="26" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="AD11" s="26" t="n">
-        <v>29.21</v>
-      </c>
-      <c r="AE11" s="26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AF11" s="26" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="AG11" s="26" t="n">
-        <v>34.25</v>
-      </c>
-      <c r="AH11" s="26" t="n">
-        <v>18.73</v>
+      <c r="AC11" s="27" t="n">
+        <v>50.36</v>
+      </c>
+      <c r="AD11" s="27" t="n">
+        <v>29.36</v>
+      </c>
+      <c r="AE11" s="27" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="AF11" s="27" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="AG11" s="27" t="n">
+        <v>33.58</v>
+      </c>
+      <c r="AH11" s="27" t="n">
+        <v>18.71</v>
       </c>
       <c r="AI11" s="27" t="n">
         <v>61.75</v>

--- a/experiments/敦煌变化数据_predicted.xlsx
+++ b/experiments/敦煌变化数据_predicted.xlsx
@@ -10559,31 +10559,31 @@
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>46.1</v>
+        <v>46.31</v>
       </c>
       <c r="C5" s="27" t="n">
-        <v>34.12</v>
+        <v>34.25</v>
       </c>
       <c r="D5" s="27" t="n">
-        <v>18.3</v>
+        <v>18.41</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>46.71</v>
+        <v>46.62</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>36.52</v>
+        <v>36.42</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>16.78</v>
+        <v>17.18</v>
       </c>
       <c r="H5" s="27" t="n">
-        <v>48.06</v>
+        <v>47.96</v>
       </c>
       <c r="I5" s="27" t="n">
-        <v>34.56</v>
+        <v>34.68</v>
       </c>
       <c r="J5" s="27" t="n">
-        <v>17.95</v>
+        <v>18.07</v>
       </c>
       <c r="K5" s="27" t="n">
         <v>59.11</v>
@@ -10640,22 +10640,22 @@
         <v>-32.94</v>
       </c>
       <c r="AC5" s="27" t="n">
-        <v>48.31</v>
+        <v>48.5</v>
       </c>
       <c r="AD5" s="27" t="n">
-        <v>34.7</v>
+        <v>34.96</v>
       </c>
       <c r="AE5" s="27" t="n">
-        <v>20.37</v>
+        <v>20.84</v>
       </c>
       <c r="AF5" s="27" t="n">
-        <v>50.09</v>
+        <v>50.38</v>
       </c>
       <c r="AG5" s="27" t="n">
-        <v>34.77</v>
+        <v>34.6</v>
       </c>
       <c r="AH5" s="27" t="n">
-        <v>19.47</v>
+        <v>19.72</v>
       </c>
       <c r="AI5" s="27" t="n">
         <v>60.77</v>
@@ -10701,31 +10701,31 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>45.61</v>
+        <v>45.78</v>
       </c>
       <c r="C6" s="27" t="n">
-        <v>33.21</v>
+        <v>33.4</v>
       </c>
       <c r="D6" s="27" t="n">
-        <v>18.29</v>
+        <v>18.19</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>46.62</v>
+        <v>46.57</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>36.61</v>
+        <v>36.64</v>
       </c>
       <c r="G6" s="27" t="n">
-        <v>16.16</v>
+        <v>16.34</v>
       </c>
       <c r="H6" s="27" t="n">
-        <v>47.55</v>
+        <v>47.5</v>
       </c>
       <c r="I6" s="27" t="n">
-        <v>33.84</v>
+        <v>33.98</v>
       </c>
       <c r="J6" s="27" t="n">
-        <v>16.73</v>
+        <v>16.74</v>
       </c>
       <c r="K6" s="27" t="n">
         <v>58.95</v>
@@ -10782,22 +10782,22 @@
         <v>-33.22</v>
       </c>
       <c r="AC6" s="27" t="n">
-        <v>48.19</v>
+        <v>48.27</v>
       </c>
       <c r="AD6" s="27" t="n">
-        <v>34.33</v>
+        <v>34.27</v>
       </c>
       <c r="AE6" s="27" t="n">
-        <v>20.35</v>
+        <v>20.14</v>
       </c>
       <c r="AF6" s="27" t="n">
-        <v>49.64</v>
+        <v>49.82</v>
       </c>
       <c r="AG6" s="27" t="n">
-        <v>34.09</v>
+        <v>33.92</v>
       </c>
       <c r="AH6" s="27" t="n">
-        <v>18.76</v>
+        <v>18.8</v>
       </c>
       <c r="AI6" s="27" t="n">
         <v>60.81</v>
@@ -10843,31 +10843,31 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>45.8</v>
+        <v>45.87</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>33.06</v>
+        <v>33.2</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>17.88</v>
+        <v>17.77</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>46.32</v>
+        <v>46.26</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>36.8</v>
+        <v>36.6</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>16.28</v>
+        <v>16.23</v>
       </c>
       <c r="H7" s="27" t="n">
-        <v>46.86</v>
+        <v>46.98</v>
       </c>
       <c r="I7" s="27" t="n">
-        <v>33.7</v>
+        <v>33.75</v>
       </c>
       <c r="J7" s="27" t="n">
-        <v>15.56</v>
+        <v>15.68</v>
       </c>
       <c r="K7" s="27" t="n">
         <v>59.05</v>
@@ -10924,22 +10924,22 @@
         <v>-33.19</v>
       </c>
       <c r="AC7" s="27" t="n">
-        <v>48.38</v>
+        <v>48.52</v>
       </c>
       <c r="AD7" s="27" t="n">
-        <v>33.73</v>
+        <v>33.52</v>
       </c>
       <c r="AE7" s="27" t="n">
-        <v>19.49</v>
+        <v>19.12</v>
       </c>
       <c r="AF7" s="27" t="n">
-        <v>49.91</v>
+        <v>49.98</v>
       </c>
       <c r="AG7" s="27" t="n">
-        <v>32.74</v>
+        <v>32.98</v>
       </c>
       <c r="AH7" s="27" t="n">
-        <v>18.22</v>
+        <v>18.27</v>
       </c>
       <c r="AI7" s="27" t="n">
         <v>61.4</v>
@@ -10985,31 +10985,31 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>46.26</v>
+        <v>46.2</v>
       </c>
       <c r="C8" s="27" t="n">
-        <v>33.48</v>
+        <v>33.47</v>
       </c>
       <c r="D8" s="27" t="n">
-        <v>17.01</v>
+        <v>17.09</v>
       </c>
       <c r="E8" s="27" t="n">
-        <v>45.79</v>
+        <v>45.83</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>36.21</v>
+        <v>35.99</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>16.19</v>
+        <v>16.14</v>
       </c>
       <c r="H8" s="27" t="n">
-        <v>46.67</v>
+        <v>46.77</v>
       </c>
       <c r="I8" s="27" t="n">
-        <v>33.75</v>
+        <v>33.73</v>
       </c>
       <c r="J8" s="27" t="n">
-        <v>14.85</v>
+        <v>15.07</v>
       </c>
       <c r="K8" s="27" t="n">
         <v>59.45</v>
@@ -11069,19 +11069,19 @@
         <v>49.11</v>
       </c>
       <c r="AD8" s="27" t="n">
-        <v>32.3</v>
+        <v>32.35</v>
       </c>
       <c r="AE8" s="27" t="n">
-        <v>17.15</v>
+        <v>17.42</v>
       </c>
       <c r="AF8" s="27" t="n">
-        <v>50.45</v>
+        <v>50.42</v>
       </c>
       <c r="AG8" s="27" t="n">
-        <v>32.34</v>
+        <v>32.62</v>
       </c>
       <c r="AH8" s="27" t="n">
-        <v>17.88</v>
+        <v>18.02</v>
       </c>
       <c r="AI8" s="27" t="n">
         <v>62.35</v>
@@ -11127,31 +11127,31 @@
         </is>
       </c>
       <c r="B9" s="27" t="n">
-        <v>46.49</v>
+        <v>46.44</v>
       </c>
       <c r="C9" s="27" t="n">
-        <v>33.84</v>
+        <v>33.7</v>
       </c>
       <c r="D9" s="27" t="n">
-        <v>16.44</v>
+        <v>16.54</v>
       </c>
       <c r="E9" s="27" t="n">
-        <v>45.43</v>
+        <v>45.44</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>34.74</v>
+        <v>34.87</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>15.89</v>
+        <v>15.88</v>
       </c>
       <c r="H9" s="27" t="n">
-        <v>46.87</v>
+        <v>46.85</v>
       </c>
       <c r="I9" s="27" t="n">
-        <v>33.74</v>
+        <v>33.71</v>
       </c>
       <c r="J9" s="27" t="n">
-        <v>15.02</v>
+        <v>15.01</v>
       </c>
       <c r="K9" s="27" t="n">
         <v>60.08</v>
@@ -11208,19 +11208,19 @@
         <v>-34.44</v>
       </c>
       <c r="AC9" s="27" t="n">
-        <v>49.85</v>
+        <v>49.75</v>
       </c>
       <c r="AD9" s="27" t="n">
-        <v>31.07</v>
+        <v>31.08</v>
       </c>
       <c r="AE9" s="27" t="n">
-        <v>15.89</v>
+        <v>15.99</v>
       </c>
       <c r="AF9" s="27" t="n">
-        <v>50.88</v>
+        <v>50.77</v>
       </c>
       <c r="AG9" s="27" t="n">
-        <v>33.06</v>
+        <v>33.03</v>
       </c>
       <c r="AH9" s="27" t="n">
         <v>18.12</v>
@@ -11272,28 +11272,28 @@
         <v>46.52</v>
       </c>
       <c r="C10" s="27" t="n">
-        <v>33.62</v>
+        <v>33.55</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>16.25</v>
+        <v>16.24</v>
       </c>
       <c r="E10" s="27" t="n">
         <v>45.1</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>33.78</v>
+        <v>34.03</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>15.56</v>
+        <v>15.57</v>
       </c>
       <c r="H10" s="27" t="n">
-        <v>46.99</v>
+        <v>46.93</v>
       </c>
       <c r="I10" s="27" t="n">
         <v>33.61</v>
       </c>
       <c r="J10" s="27" t="n">
-        <v>15.16</v>
+        <v>15.07</v>
       </c>
       <c r="K10" s="27" t="n">
         <v>60.75</v>
@@ -11349,23 +11349,23 @@
       <c r="AB10" s="27" t="n">
         <v>-33.95</v>
       </c>
-      <c r="AC10" s="26" t="n">
-        <v>50.18</v>
+      <c r="AC10" s="27" t="n">
+        <v>50.14</v>
       </c>
       <c r="AD10" s="27" t="n">
-        <v>29.88</v>
+        <v>30.05</v>
       </c>
       <c r="AE10" s="27" t="n">
-        <v>15.04</v>
+        <v>15.14</v>
       </c>
       <c r="AF10" s="27" t="n">
-        <v>50.87</v>
+        <v>50.83</v>
       </c>
       <c r="AG10" s="27" t="n">
-        <v>33.66</v>
+        <v>33.49</v>
       </c>
       <c r="AH10" s="27" t="n">
-        <v>18.37</v>
+        <v>18.39</v>
       </c>
       <c r="AI10" s="27" t="n">
         <v>60.93</v>
@@ -11411,22 +11411,22 @@
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>46.54</v>
+        <v>46.51</v>
       </c>
       <c r="C11" s="27" t="n">
-        <v>33.13</v>
+        <v>33.19</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>16.04</v>
+        <v>16.03</v>
       </c>
       <c r="E11" s="27" t="n">
-        <v>44.79</v>
+        <v>44.97</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>33.8</v>
+        <v>33.82</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>15.27</v>
+        <v>15.21</v>
       </c>
       <c r="H11" s="27" t="n">
         <v>46.86</v>
@@ -11435,7 +11435,7 @@
         <v>33.49</v>
       </c>
       <c r="J11" s="27" t="n">
-        <v>14.93</v>
+        <v>14.95</v>
       </c>
       <c r="K11" s="27" t="n">
         <v>60.94</v>
@@ -11492,22 +11492,22 @@
         <v>-31.7</v>
       </c>
       <c r="AC11" s="27" t="n">
-        <v>50.36</v>
+        <v>50.32</v>
       </c>
       <c r="AD11" s="27" t="n">
-        <v>29.36</v>
+        <v>29.6</v>
       </c>
       <c r="AE11" s="27" t="n">
-        <v>14.6</v>
+        <v>15.4</v>
       </c>
       <c r="AF11" s="27" t="n">
-        <v>50.71</v>
+        <v>50.77</v>
       </c>
       <c r="AG11" s="27" t="n">
-        <v>33.58</v>
+        <v>33.3</v>
       </c>
       <c r="AH11" s="27" t="n">
-        <v>18.71</v>
+        <v>18.76</v>
       </c>
       <c r="AI11" s="27" t="n">
         <v>61.75</v>

--- a/experiments/敦煌变化数据_predicted.xlsx
+++ b/experiments/敦煌变化数据_predicted.xlsx
@@ -10559,31 +10559,31 @@
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>46.31</v>
+        <v>46.46</v>
       </c>
       <c r="C5" s="27" t="n">
-        <v>34.25</v>
+        <v>34.37</v>
       </c>
       <c r="D5" s="27" t="n">
-        <v>18.41</v>
+        <v>18.43</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>46.62</v>
+        <v>46.56</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>36.42</v>
+        <v>36.38</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>17.18</v>
+        <v>17.43</v>
       </c>
       <c r="H5" s="27" t="n">
-        <v>47.96</v>
+        <v>47.89</v>
       </c>
       <c r="I5" s="27" t="n">
-        <v>34.68</v>
+        <v>34.77</v>
       </c>
       <c r="J5" s="27" t="n">
-        <v>18.07</v>
+        <v>18.13</v>
       </c>
       <c r="K5" s="27" t="n">
         <v>59.11</v>
@@ -10640,22 +10640,22 @@
         <v>-32.94</v>
       </c>
       <c r="AC5" s="27" t="n">
-        <v>48.5</v>
+        <v>48.62</v>
       </c>
       <c r="AD5" s="27" t="n">
-        <v>34.96</v>
+        <v>35.07</v>
       </c>
       <c r="AE5" s="27" t="n">
-        <v>20.84</v>
+        <v>21.02</v>
       </c>
       <c r="AF5" s="27" t="n">
-        <v>50.38</v>
+        <v>50.56</v>
       </c>
       <c r="AG5" s="27" t="n">
-        <v>34.6</v>
+        <v>34.47</v>
       </c>
       <c r="AH5" s="27" t="n">
-        <v>19.72</v>
+        <v>19.86</v>
       </c>
       <c r="AI5" s="27" t="n">
         <v>60.77</v>
@@ -10701,31 +10701,31 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>45.78</v>
+        <v>45.94</v>
       </c>
       <c r="C6" s="27" t="n">
-        <v>33.4</v>
+        <v>33.56</v>
       </c>
       <c r="D6" s="27" t="n">
-        <v>18.19</v>
+        <v>18.14</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>46.57</v>
+        <v>46.5</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>36.64</v>
+        <v>36.58</v>
       </c>
       <c r="G6" s="27" t="n">
-        <v>16.34</v>
+        <v>16.52</v>
       </c>
       <c r="H6" s="27" t="n">
-        <v>47.5</v>
+        <v>47.48</v>
       </c>
       <c r="I6" s="27" t="n">
-        <v>33.98</v>
+        <v>34.1</v>
       </c>
       <c r="J6" s="27" t="n">
-        <v>16.74</v>
+        <v>16.81</v>
       </c>
       <c r="K6" s="27" t="n">
         <v>58.95</v>
@@ -10782,22 +10782,22 @@
         <v>-33.22</v>
       </c>
       <c r="AC6" s="27" t="n">
-        <v>48.27</v>
+        <v>48.39</v>
       </c>
       <c r="AD6" s="27" t="n">
-        <v>34.27</v>
+        <v>34.26</v>
       </c>
       <c r="AE6" s="27" t="n">
-        <v>20.14</v>
+        <v>20.06</v>
       </c>
       <c r="AF6" s="27" t="n">
-        <v>49.82</v>
+        <v>50</v>
       </c>
       <c r="AG6" s="27" t="n">
-        <v>33.92</v>
+        <v>33.85</v>
       </c>
       <c r="AH6" s="27" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AI6" s="27" t="n">
         <v>60.81</v>
@@ -10843,31 +10843,31 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>45.87</v>
+        <v>45.93</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>33.2</v>
+        <v>33.32</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>17.77</v>
+        <v>17.71</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>46.26</v>
+        <v>46.23</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>36.6</v>
+        <v>36.46</v>
       </c>
       <c r="G7" s="27" t="n">
         <v>16.23</v>
       </c>
       <c r="H7" s="27" t="n">
-        <v>46.98</v>
+        <v>47.06</v>
       </c>
       <c r="I7" s="27" t="n">
-        <v>33.75</v>
+        <v>33.8</v>
       </c>
       <c r="J7" s="27" t="n">
-        <v>15.68</v>
+        <v>15.79</v>
       </c>
       <c r="K7" s="27" t="n">
         <v>59.05</v>
@@ -10924,22 +10924,22 @@
         <v>-33.19</v>
       </c>
       <c r="AC7" s="27" t="n">
-        <v>48.52</v>
+        <v>48.61</v>
       </c>
       <c r="AD7" s="27" t="n">
-        <v>33.52</v>
+        <v>33.41</v>
       </c>
       <c r="AE7" s="27" t="n">
-        <v>19.12</v>
+        <v>18.95</v>
       </c>
       <c r="AF7" s="27" t="n">
-        <v>49.98</v>
+        <v>50.05</v>
       </c>
       <c r="AG7" s="27" t="n">
-        <v>32.98</v>
+        <v>33.12</v>
       </c>
       <c r="AH7" s="27" t="n">
-        <v>18.27</v>
+        <v>18.34</v>
       </c>
       <c r="AI7" s="27" t="n">
         <v>61.4</v>
@@ -10985,31 +10985,31 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>46.2</v>
+        <v>46.18</v>
       </c>
       <c r="C8" s="27" t="n">
-        <v>33.47</v>
+        <v>33.46</v>
       </c>
       <c r="D8" s="27" t="n">
-        <v>17.09</v>
+        <v>17.12</v>
       </c>
       <c r="E8" s="27" t="n">
-        <v>45.83</v>
+        <v>45.84</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>35.99</v>
+        <v>35.86</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>16.14</v>
+        <v>16.1</v>
       </c>
       <c r="H8" s="27" t="n">
-        <v>46.77</v>
+        <v>46.84</v>
       </c>
       <c r="I8" s="27" t="n">
         <v>33.73</v>
       </c>
       <c r="J8" s="27" t="n">
-        <v>15.07</v>
+        <v>15.21</v>
       </c>
       <c r="K8" s="27" t="n">
         <v>59.45</v>
@@ -11066,22 +11066,22 @@
         <v>-33.64</v>
       </c>
       <c r="AC8" s="27" t="n">
-        <v>49.11</v>
+        <v>49.12</v>
       </c>
       <c r="AD8" s="27" t="n">
-        <v>32.35</v>
+        <v>32.33</v>
       </c>
       <c r="AE8" s="27" t="n">
-        <v>17.42</v>
+        <v>17.49</v>
       </c>
       <c r="AF8" s="27" t="n">
-        <v>50.42</v>
+        <v>50.4</v>
       </c>
       <c r="AG8" s="27" t="n">
-        <v>32.62</v>
+        <v>32.81</v>
       </c>
       <c r="AH8" s="27" t="n">
-        <v>18.02</v>
+        <v>18.11</v>
       </c>
       <c r="AI8" s="27" t="n">
         <v>62.35</v>
@@ -11127,31 +11127,31 @@
         </is>
       </c>
       <c r="B9" s="27" t="n">
-        <v>46.44</v>
+        <v>46.4</v>
       </c>
       <c r="C9" s="27" t="n">
-        <v>33.7</v>
+        <v>33.61</v>
       </c>
       <c r="D9" s="27" t="n">
-        <v>16.54</v>
+        <v>16.6</v>
       </c>
       <c r="E9" s="27" t="n">
-        <v>45.44</v>
+        <v>45.45</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>34.87</v>
+        <v>34.94</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>15.88</v>
+        <v>15.87</v>
       </c>
       <c r="H9" s="27" t="n">
         <v>46.85</v>
       </c>
       <c r="I9" s="27" t="n">
-        <v>33.71</v>
+        <v>33.69</v>
       </c>
       <c r="J9" s="27" t="n">
-        <v>15.01</v>
+        <v>15.04</v>
       </c>
       <c r="K9" s="27" t="n">
         <v>60.08</v>
@@ -11208,22 +11208,22 @@
         <v>-34.44</v>
       </c>
       <c r="AC9" s="27" t="n">
-        <v>49.75</v>
+        <v>49.69</v>
       </c>
       <c r="AD9" s="27" t="n">
-        <v>31.08</v>
+        <v>31.14</v>
       </c>
       <c r="AE9" s="27" t="n">
-        <v>15.99</v>
+        <v>16.14</v>
       </c>
       <c r="AF9" s="27" t="n">
-        <v>50.77</v>
+        <v>50.7</v>
       </c>
       <c r="AG9" s="27" t="n">
-        <v>33.03</v>
+        <v>33.04</v>
       </c>
       <c r="AH9" s="27" t="n">
-        <v>18.12</v>
+        <v>18.16</v>
       </c>
       <c r="AI9" s="27" t="n">
         <v>61.81</v>
@@ -11269,31 +11269,31 @@
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>46.52</v>
+        <v>46.5</v>
       </c>
       <c r="C10" s="27" t="n">
-        <v>33.55</v>
+        <v>33.5</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>16.24</v>
+        <v>16.26</v>
       </c>
       <c r="E10" s="27" t="n">
-        <v>45.1</v>
+        <v>45.15</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>34.03</v>
+        <v>34.19</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>15.57</v>
+        <v>15.56</v>
       </c>
       <c r="H10" s="27" t="n">
-        <v>46.93</v>
+        <v>46.89</v>
       </c>
       <c r="I10" s="27" t="n">
         <v>33.61</v>
       </c>
       <c r="J10" s="27" t="n">
-        <v>15.07</v>
+        <v>15.02</v>
       </c>
       <c r="K10" s="27" t="n">
         <v>60.75</v>
@@ -11350,22 +11350,22 @@
         <v>-33.95</v>
       </c>
       <c r="AC10" s="27" t="n">
-        <v>50.14</v>
+        <v>50.09</v>
       </c>
       <c r="AD10" s="27" t="n">
-        <v>30.05</v>
+        <v>30.2</v>
       </c>
       <c r="AE10" s="27" t="n">
-        <v>15.14</v>
+        <v>15.42</v>
       </c>
       <c r="AF10" s="27" t="n">
-        <v>50.83</v>
+        <v>50.8</v>
       </c>
       <c r="AG10" s="27" t="n">
-        <v>33.49</v>
+        <v>33.33</v>
       </c>
       <c r="AH10" s="27" t="n">
-        <v>18.39</v>
+        <v>18.42</v>
       </c>
       <c r="AI10" s="27" t="n">
         <v>60.93</v>
@@ -11411,31 +11411,31 @@
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>46.51</v>
+        <v>46.49</v>
       </c>
       <c r="C11" s="27" t="n">
-        <v>33.19</v>
+        <v>33.2</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>16.03</v>
+        <v>16.02</v>
       </c>
       <c r="E11" s="27" t="n">
-        <v>44.97</v>
+        <v>45.06</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>33.82</v>
+        <v>33.89</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>15.21</v>
+        <v>15.18</v>
       </c>
       <c r="H11" s="27" t="n">
-        <v>46.86</v>
+        <v>46.84</v>
       </c>
       <c r="I11" s="27" t="n">
         <v>33.49</v>
       </c>
       <c r="J11" s="27" t="n">
-        <v>14.95</v>
+        <v>14.93</v>
       </c>
       <c r="K11" s="27" t="n">
         <v>60.94</v>
@@ -11492,22 +11492,22 @@
         <v>-31.7</v>
       </c>
       <c r="AC11" s="27" t="n">
-        <v>50.32</v>
+        <v>50.29</v>
       </c>
       <c r="AD11" s="27" t="n">
-        <v>29.6</v>
+        <v>29.76</v>
       </c>
       <c r="AE11" s="27" t="n">
-        <v>15.4</v>
+        <v>15.82</v>
       </c>
       <c r="AF11" s="27" t="n">
-        <v>50.77</v>
+        <v>50.8</v>
       </c>
       <c r="AG11" s="27" t="n">
-        <v>33.3</v>
+        <v>33.12</v>
       </c>
       <c r="AH11" s="27" t="n">
-        <v>18.76</v>
+        <v>18.79</v>
       </c>
       <c r="AI11" s="27" t="n">
         <v>61.75</v>

--- a/experiments/敦煌变化数据_predicted.xlsx
+++ b/experiments/敦煌变化数据_predicted.xlsx
@@ -10559,139 +10559,139 @@
         </is>
       </c>
       <c r="B5" s="27" t="n">
-        <v>46.46</v>
+        <v>44.45</v>
       </c>
       <c r="C5" s="27" t="n">
-        <v>34.37</v>
+        <v>31.95</v>
       </c>
       <c r="D5" s="27" t="n">
-        <v>18.43</v>
+        <v>17.82</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>46.56</v>
+        <v>46.78</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>36.38</v>
+        <v>37.05</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>17.43</v>
+        <v>14.24</v>
       </c>
       <c r="H5" s="27" t="n">
-        <v>47.89</v>
+        <v>47.34</v>
       </c>
       <c r="I5" s="27" t="n">
-        <v>34.77</v>
+        <v>32.8</v>
       </c>
       <c r="J5" s="27" t="n">
-        <v>18.13</v>
+        <v>15.04</v>
       </c>
       <c r="K5" s="27" t="n">
-        <v>59.11</v>
+        <v>57.67</v>
       </c>
       <c r="L5" s="27" t="n">
-        <v>-32.14</v>
+        <v>-32.97</v>
       </c>
       <c r="M5" s="27" t="n">
-        <v>15.47</v>
+        <v>15.94</v>
       </c>
       <c r="N5" s="27" t="n">
-        <v>58.16</v>
+        <v>55.91</v>
       </c>
       <c r="O5" s="27" t="n">
-        <v>-32.2</v>
+        <v>-31.83</v>
       </c>
       <c r="P5" s="27" t="n">
-        <v>16.09</v>
+        <v>18.83</v>
       </c>
       <c r="Q5" s="27" t="n">
-        <v>61.24</v>
+        <v>65.83</v>
       </c>
       <c r="R5" s="27" t="n">
-        <v>-32.28</v>
+        <v>-32.75</v>
       </c>
       <c r="S5" s="27" t="n">
-        <v>13.16</v>
+        <v>7.43</v>
       </c>
       <c r="T5" s="27" t="n">
-        <v>40.73</v>
+        <v>39.37</v>
       </c>
       <c r="U5" s="27" t="n">
-        <v>-5.36</v>
+        <v>-5.48</v>
       </c>
       <c r="V5" s="27" t="n">
         <v>-32.75</v>
       </c>
       <c r="W5" s="27" t="n">
-        <v>40.27</v>
+        <v>39.78</v>
       </c>
       <c r="X5" s="27" t="n">
-        <v>-5.63</v>
+        <v>-7.03</v>
       </c>
       <c r="Y5" s="27" t="n">
-        <v>-31.91</v>
+        <v>-29.47</v>
       </c>
       <c r="Z5" s="27" t="n">
-        <v>40.67</v>
+        <v>40.79</v>
       </c>
       <c r="AA5" s="27" t="n">
-        <v>-5.25</v>
+        <v>-4.86</v>
       </c>
       <c r="AB5" s="27" t="n">
-        <v>-32.94</v>
+        <v>-34.4</v>
       </c>
       <c r="AC5" s="27" t="n">
-        <v>48.62</v>
+        <v>47.44</v>
       </c>
       <c r="AD5" s="27" t="n">
-        <v>35.07</v>
+        <v>32.98</v>
       </c>
       <c r="AE5" s="27" t="n">
-        <v>21.02</v>
+        <v>18.52</v>
       </c>
       <c r="AF5" s="27" t="n">
-        <v>50.56</v>
+        <v>48.28</v>
       </c>
       <c r="AG5" s="27" t="n">
-        <v>34.47</v>
+        <v>33.86</v>
       </c>
       <c r="AH5" s="27" t="n">
-        <v>19.86</v>
+        <v>17.18</v>
       </c>
       <c r="AI5" s="27" t="n">
-        <v>60.77</v>
+        <v>62.72</v>
       </c>
       <c r="AJ5" s="27" t="n">
-        <v>-31.25</v>
+        <v>-29.4</v>
       </c>
       <c r="AK5" s="27" t="n">
-        <v>15.29</v>
+        <v>14.4</v>
       </c>
       <c r="AL5" s="27" t="n">
-        <v>62.72</v>
+        <v>62.48</v>
       </c>
       <c r="AM5" s="27" t="n">
-        <v>-30.77</v>
+        <v>-31.38</v>
       </c>
       <c r="AN5" s="27" t="n">
-        <v>14.1</v>
+        <v>14.51</v>
       </c>
       <c r="AO5" s="27" t="n">
-        <v>38.59</v>
+        <v>33.35</v>
       </c>
       <c r="AP5" s="27" t="n">
-        <v>-6.23</v>
+        <v>-10.52</v>
       </c>
       <c r="AQ5" s="27" t="n">
-        <v>-28.29</v>
+        <v>-26.95</v>
       </c>
       <c r="AR5" s="27" t="n">
-        <v>39.19</v>
+        <v>39.41</v>
       </c>
       <c r="AS5" s="27" t="n">
-        <v>-7.2</v>
+        <v>-9.56</v>
       </c>
       <c r="AT5" s="27" t="n">
-        <v>-27.58</v>
+        <v>-26.22</v>
       </c>
     </row>
     <row r="6">
@@ -10701,139 +10701,139 @@
         </is>
       </c>
       <c r="B6" s="27" t="n">
-        <v>45.94</v>
+        <v>42.87</v>
       </c>
       <c r="C6" s="27" t="n">
-        <v>33.56</v>
+        <v>29.5</v>
       </c>
       <c r="D6" s="27" t="n">
-        <v>18.14</v>
+        <v>16.94</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>46.5</v>
+        <v>46.6</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>36.58</v>
+        <v>37.66</v>
       </c>
       <c r="G6" s="27" t="n">
-        <v>16.52</v>
+        <v>11.48</v>
       </c>
       <c r="H6" s="27" t="n">
-        <v>47.48</v>
+        <v>46.1</v>
       </c>
       <c r="I6" s="27" t="n">
-        <v>34.1</v>
+        <v>30.77</v>
       </c>
       <c r="J6" s="27" t="n">
-        <v>16.81</v>
+        <v>11.04</v>
       </c>
       <c r="K6" s="27" t="n">
-        <v>58.95</v>
+        <v>57.18</v>
       </c>
       <c r="L6" s="27" t="n">
-        <v>-31.72</v>
+        <v>-31.7</v>
       </c>
       <c r="M6" s="27" t="n">
-        <v>15.58</v>
+        <v>16.27</v>
       </c>
       <c r="N6" s="27" t="n">
-        <v>57.96</v>
+        <v>55.3</v>
       </c>
       <c r="O6" s="27" t="n">
-        <v>-32.66</v>
+        <v>-33.23</v>
       </c>
       <c r="P6" s="27" t="n">
-        <v>16.53</v>
+        <v>20.17</v>
       </c>
       <c r="Q6" s="27" t="n">
-        <v>61.17</v>
+        <v>65.62</v>
       </c>
       <c r="R6" s="27" t="n">
-        <v>-32.24</v>
+        <v>-32.63</v>
       </c>
       <c r="S6" s="27" t="n">
-        <v>12.81</v>
+        <v>6.37</v>
       </c>
       <c r="T6" s="27" t="n">
-        <v>40.21</v>
+        <v>37.79</v>
       </c>
       <c r="U6" s="27" t="n">
-        <v>-5.44</v>
+        <v>-5.72</v>
       </c>
       <c r="V6" s="27" t="n">
-        <v>-32.61</v>
+        <v>-32.33</v>
       </c>
       <c r="W6" s="27" t="n">
+        <v>39.63</v>
+      </c>
+      <c r="X6" s="27" t="n">
+        <v>-6.88</v>
+      </c>
+      <c r="Y6" s="27" t="n">
+        <v>-29.71</v>
+      </c>
+      <c r="Z6" s="27" t="n">
         <v>40.22</v>
       </c>
-      <c r="X6" s="27" t="n">
-        <v>-5.58</v>
-      </c>
-      <c r="Y6" s="27" t="n">
-        <v>-31.99</v>
-      </c>
-      <c r="Z6" s="27" t="n">
-        <v>40.48</v>
-      </c>
       <c r="AA6" s="27" t="n">
-        <v>-5.28</v>
+        <v>-4.95</v>
       </c>
       <c r="AB6" s="27" t="n">
-        <v>-33.22</v>
+        <v>-35.25</v>
       </c>
       <c r="AC6" s="27" t="n">
-        <v>48.39</v>
+        <v>46.74</v>
       </c>
       <c r="AD6" s="27" t="n">
-        <v>34.26</v>
+        <v>30.52</v>
       </c>
       <c r="AE6" s="27" t="n">
-        <v>20.06</v>
+        <v>15.61</v>
       </c>
       <c r="AF6" s="27" t="n">
-        <v>50</v>
+        <v>46.59</v>
       </c>
       <c r="AG6" s="27" t="n">
-        <v>33.85</v>
+        <v>31.98</v>
       </c>
       <c r="AH6" s="27" t="n">
-        <v>18.9</v>
+        <v>14.27</v>
       </c>
       <c r="AI6" s="27" t="n">
-        <v>60.81</v>
+        <v>62.84</v>
       </c>
       <c r="AJ6" s="27" t="n">
-        <v>-30.92</v>
+        <v>-28.4</v>
       </c>
       <c r="AK6" s="27" t="n">
-        <v>14.95</v>
+        <v>13.37</v>
       </c>
       <c r="AL6" s="27" t="n">
-        <v>62.66</v>
+        <v>62.29</v>
       </c>
       <c r="AM6" s="27" t="n">
-        <v>-30.83</v>
+        <v>-31.56</v>
       </c>
       <c r="AN6" s="27" t="n">
-        <v>14.25</v>
+        <v>14.96</v>
       </c>
       <c r="AO6" s="27" t="n">
-        <v>38.19</v>
+        <v>32.14</v>
       </c>
       <c r="AP6" s="27" t="n">
-        <v>-6.51</v>
+        <v>-11.37</v>
       </c>
       <c r="AQ6" s="27" t="n">
-        <v>-27.75</v>
+        <v>-25.31</v>
       </c>
       <c r="AR6" s="27" t="n">
-        <v>38.8</v>
+        <v>38.23</v>
       </c>
       <c r="AS6" s="27" t="n">
-        <v>-7.68</v>
+        <v>-11.01</v>
       </c>
       <c r="AT6" s="27" t="n">
-        <v>-27.69</v>
+        <v>-26.55</v>
       </c>
     </row>
     <row r="7">
@@ -10843,139 +10843,139 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>45.93</v>
+        <v>42.84</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>33.32</v>
+        <v>28.77</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>17.71</v>
+        <v>15.64</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>46.23</v>
+        <v>45.78</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>36.46</v>
+        <v>37.29</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>16.23</v>
+        <v>10.6</v>
       </c>
       <c r="H7" s="27" t="n">
-        <v>47.06</v>
+        <v>44.83</v>
       </c>
       <c r="I7" s="27" t="n">
-        <v>33.8</v>
+        <v>29.86</v>
       </c>
       <c r="J7" s="27" t="n">
-        <v>15.79</v>
+        <v>7.95</v>
       </c>
       <c r="K7" s="27" t="n">
-        <v>59.05</v>
+        <v>57.49</v>
       </c>
       <c r="L7" s="27" t="n">
-        <v>-31.03</v>
+        <v>-29.61</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>15.18</v>
+        <v>15.06</v>
       </c>
       <c r="N7" s="27" t="n">
-        <v>57.81</v>
+        <v>54.84</v>
       </c>
       <c r="O7" s="27" t="n">
-        <v>-32.9</v>
+        <v>-33.96</v>
       </c>
       <c r="P7" s="27" t="n">
-        <v>16.36</v>
+        <v>19.65</v>
       </c>
       <c r="Q7" s="27" t="n">
-        <v>59.96</v>
+        <v>61.95</v>
       </c>
       <c r="R7" s="27" t="n">
-        <v>-31.72</v>
+        <v>-31.05</v>
       </c>
       <c r="S7" s="27" t="n">
-        <v>12.26</v>
+        <v>4.7</v>
       </c>
       <c r="T7" s="27" t="n">
-        <v>40.41</v>
+        <v>38.4</v>
       </c>
       <c r="U7" s="27" t="n">
-        <v>-5.25</v>
+        <v>-5.15</v>
       </c>
       <c r="V7" s="27" t="n">
-        <v>-32.19</v>
+        <v>-31.05</v>
       </c>
       <c r="W7" s="27" t="n">
-        <v>40.42</v>
+        <v>40.24</v>
       </c>
       <c r="X7" s="27" t="n">
-        <v>-5.22</v>
+        <v>-5.79</v>
       </c>
       <c r="Y7" s="27" t="n">
-        <v>-32.48</v>
+        <v>-31.2</v>
       </c>
       <c r="Z7" s="27" t="n">
-        <v>40.87</v>
+        <v>41.4</v>
       </c>
       <c r="AA7" s="27" t="n">
-        <v>-5.15</v>
+        <v>-4.56</v>
       </c>
       <c r="AB7" s="27" t="n">
-        <v>-33.19</v>
+        <v>-35.16</v>
       </c>
       <c r="AC7" s="27" t="n">
-        <v>48.61</v>
+        <v>47.41</v>
       </c>
       <c r="AD7" s="27" t="n">
-        <v>33.41</v>
+        <v>27.95</v>
       </c>
       <c r="AE7" s="27" t="n">
-        <v>18.95</v>
+        <v>12.25</v>
       </c>
       <c r="AF7" s="27" t="n">
-        <v>50.05</v>
+        <v>46.74</v>
       </c>
       <c r="AG7" s="27" t="n">
-        <v>33.12</v>
+        <v>29.77</v>
       </c>
       <c r="AH7" s="27" t="n">
-        <v>18.34</v>
+        <v>12.57</v>
       </c>
       <c r="AI7" s="27" t="n">
-        <v>61.4</v>
+        <v>64.63</v>
       </c>
       <c r="AJ7" s="27" t="n">
-        <v>-30.74</v>
+        <v>-27.86</v>
       </c>
       <c r="AK7" s="27" t="n">
-        <v>14.86</v>
+        <v>13.09</v>
       </c>
       <c r="AL7" s="27" t="n">
-        <v>62.62</v>
+        <v>62.17</v>
       </c>
       <c r="AM7" s="27" t="n">
-        <v>-30.87</v>
+        <v>-31.68</v>
       </c>
       <c r="AN7" s="27" t="n">
-        <v>14.45</v>
+        <v>15.57</v>
       </c>
       <c r="AO7" s="27" t="n">
-        <v>39.69</v>
+        <v>36.68</v>
       </c>
       <c r="AP7" s="27" t="n">
-        <v>-6.76</v>
+        <v>-12.12</v>
       </c>
       <c r="AQ7" s="27" t="n">
-        <v>-26.33</v>
+        <v>-21.01</v>
       </c>
       <c r="AR7" s="27" t="n">
-        <v>36.68</v>
+        <v>31.8</v>
       </c>
       <c r="AS7" s="27" t="n">
-        <v>-7.09</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="AT7" s="27" t="n">
-        <v>-28.78</v>
+        <v>-29.86</v>
       </c>
     </row>
     <row r="8">
@@ -10985,139 +10985,139 @@
         </is>
       </c>
       <c r="B8" s="27" t="n">
-        <v>46.18</v>
+        <v>43.6</v>
       </c>
       <c r="C8" s="27" t="n">
-        <v>33.46</v>
+        <v>29.19</v>
       </c>
       <c r="D8" s="27" t="n">
-        <v>17.12</v>
+        <v>13.85</v>
       </c>
       <c r="E8" s="27" t="n">
-        <v>45.84</v>
+        <v>44.6</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>35.86</v>
+        <v>35.47</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>16.1</v>
+        <v>10.21</v>
       </c>
       <c r="H8" s="27" t="n">
-        <v>46.84</v>
+        <v>44.16</v>
       </c>
       <c r="I8" s="27" t="n">
-        <v>33.73</v>
+        <v>29.65</v>
       </c>
       <c r="J8" s="27" t="n">
-        <v>15.21</v>
+        <v>6.19</v>
       </c>
       <c r="K8" s="27" t="n">
-        <v>59.45</v>
+        <v>58.7</v>
       </c>
       <c r="L8" s="27" t="n">
-        <v>-31.11</v>
+        <v>-29.85</v>
       </c>
       <c r="M8" s="27" t="n">
-        <v>15.02</v>
+        <v>14.57</v>
       </c>
       <c r="N8" s="27" t="n">
-        <v>57.84</v>
+        <v>54.94</v>
       </c>
       <c r="O8" s="27" t="n">
-        <v>-32.73</v>
+        <v>-33.44</v>
       </c>
       <c r="P8" s="27" t="n">
-        <v>16.12</v>
+        <v>18.92</v>
       </c>
       <c r="Q8" s="27" t="n">
-        <v>59.6</v>
+        <v>60.86</v>
       </c>
       <c r="R8" s="27" t="n">
-        <v>-30.73</v>
+        <v>-28.05</v>
       </c>
       <c r="S8" s="27" t="n">
-        <v>14.08</v>
+        <v>10.22</v>
       </c>
       <c r="T8" s="27" t="n">
-        <v>41.58</v>
+        <v>41.95</v>
       </c>
       <c r="U8" s="27" t="n">
-        <v>-5.39</v>
+        <v>-5.57</v>
       </c>
       <c r="V8" s="27" t="n">
-        <v>-31.39</v>
+        <v>-28.63</v>
       </c>
       <c r="W8" s="27" t="n">
-        <v>40.88</v>
+        <v>41.63</v>
       </c>
       <c r="X8" s="27" t="n">
-        <v>-5.12</v>
+        <v>-5.49</v>
       </c>
       <c r="Y8" s="27" t="n">
-        <v>-32.63</v>
+        <v>-31.65</v>
       </c>
       <c r="Z8" s="27" t="n">
-        <v>41.49</v>
+        <v>43.28</v>
       </c>
       <c r="AA8" s="27" t="n">
-        <v>-4.48</v>
+        <v>-2.53</v>
       </c>
       <c r="AB8" s="27" t="n">
-        <v>-33.64</v>
+        <v>-36.52</v>
       </c>
       <c r="AC8" s="27" t="n">
-        <v>49.12</v>
+        <v>48.96</v>
       </c>
       <c r="AD8" s="27" t="n">
-        <v>32.33</v>
+        <v>24.67</v>
       </c>
       <c r="AE8" s="27" t="n">
-        <v>17.49</v>
+        <v>7.82</v>
       </c>
       <c r="AF8" s="27" t="n">
-        <v>50.4</v>
+        <v>47.8</v>
       </c>
       <c r="AG8" s="27" t="n">
-        <v>32.81</v>
+        <v>28.83</v>
       </c>
       <c r="AH8" s="27" t="n">
-        <v>18.11</v>
+        <v>11.87</v>
       </c>
       <c r="AI8" s="27" t="n">
-        <v>62.35</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="AJ8" s="27" t="n">
-        <v>-30.21</v>
+        <v>-26.25</v>
       </c>
       <c r="AK8" s="27" t="n">
-        <v>14.01</v>
+        <v>10.52</v>
       </c>
       <c r="AL8" s="27" t="n">
-        <v>62.69</v>
+        <v>62.39</v>
       </c>
       <c r="AM8" s="27" t="n">
-        <v>-30.78</v>
+        <v>-31.41</v>
       </c>
       <c r="AN8" s="27" t="n">
-        <v>14.39</v>
+        <v>15.39</v>
       </c>
       <c r="AO8" s="27" t="n">
-        <v>40.34</v>
+        <v>38.65</v>
       </c>
       <c r="AP8" s="27" t="n">
-        <v>-7.53</v>
+        <v>-14.46</v>
       </c>
       <c r="AQ8" s="27" t="n">
-        <v>-25.43</v>
+        <v>-18.28</v>
       </c>
       <c r="AR8" s="27" t="n">
-        <v>35.77</v>
+        <v>29.05</v>
       </c>
       <c r="AS8" s="27" t="n">
-        <v>-6.69</v>
+        <v>-8.01</v>
       </c>
       <c r="AT8" s="27" t="n">
-        <v>-29.74</v>
+        <v>-32.77</v>
       </c>
     </row>
     <row r="9">
@@ -11127,139 +11127,139 @@
         </is>
       </c>
       <c r="B9" s="27" t="n">
-        <v>46.4</v>
+        <v>44.27</v>
       </c>
       <c r="C9" s="27" t="n">
-        <v>33.61</v>
+        <v>29.65</v>
       </c>
       <c r="D9" s="27" t="n">
-        <v>16.6</v>
+        <v>12.27</v>
       </c>
       <c r="E9" s="27" t="n">
-        <v>45.45</v>
+        <v>43.42</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>34.94</v>
+        <v>32.69</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>15.87</v>
+        <v>9.51</v>
       </c>
       <c r="H9" s="27" t="n">
-        <v>46.85</v>
+        <v>44.19</v>
       </c>
       <c r="I9" s="27" t="n">
-        <v>33.69</v>
+        <v>29.53</v>
       </c>
       <c r="J9" s="27" t="n">
-        <v>15.04</v>
+        <v>5.68</v>
       </c>
       <c r="K9" s="27" t="n">
-        <v>60.08</v>
+        <v>60.61</v>
       </c>
       <c r="L9" s="27" t="n">
-        <v>-31.51</v>
+        <v>-31.06</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>14.78</v>
+        <v>13.85</v>
       </c>
       <c r="N9" s="27" t="n">
-        <v>58.19</v>
+        <v>56</v>
       </c>
       <c r="O9" s="27" t="n">
-        <v>-32.68</v>
+        <v>-33.29</v>
       </c>
       <c r="P9" s="27" t="n">
-        <v>16.21</v>
+        <v>19.2</v>
       </c>
       <c r="Q9" s="27" t="n">
-        <v>61.01</v>
+        <v>65.13</v>
       </c>
       <c r="R9" s="27" t="n">
-        <v>-29.28</v>
+        <v>-23.65</v>
       </c>
       <c r="S9" s="27" t="n">
-        <v>15.82</v>
+        <v>15.49</v>
       </c>
       <c r="T9" s="27" t="n">
-        <v>42.67</v>
+        <v>45.25</v>
       </c>
       <c r="U9" s="27" t="n">
-        <v>-5.87</v>
+        <v>-7.03</v>
       </c>
       <c r="V9" s="27" t="n">
-        <v>-30.53</v>
+        <v>-26.02</v>
       </c>
       <c r="W9" s="27" t="n">
-        <v>41.2</v>
+        <v>42.6</v>
       </c>
       <c r="X9" s="27" t="n">
-        <v>-5.15</v>
+        <v>-5.58</v>
       </c>
       <c r="Y9" s="27" t="n">
-        <v>-32.73</v>
+        <v>-31.96</v>
       </c>
       <c r="Z9" s="27" t="n">
-        <v>41.4</v>
+        <v>43</v>
       </c>
       <c r="AA9" s="27" t="n">
-        <v>-4.21</v>
+        <v>-1.71</v>
       </c>
       <c r="AB9" s="27" t="n">
-        <v>-34.44</v>
+        <v>-38.95</v>
       </c>
       <c r="AC9" s="27" t="n">
-        <v>49.69</v>
+        <v>50.69</v>
       </c>
       <c r="AD9" s="27" t="n">
-        <v>31.14</v>
+        <v>21.06</v>
       </c>
       <c r="AE9" s="27" t="n">
-        <v>16.14</v>
+        <v>3.73</v>
       </c>
       <c r="AF9" s="27" t="n">
-        <v>50.7</v>
+        <v>48.71</v>
       </c>
       <c r="AG9" s="27" t="n">
-        <v>33.04</v>
+        <v>29.53</v>
       </c>
       <c r="AH9" s="27" t="n">
-        <v>18.16</v>
+        <v>12.03</v>
       </c>
       <c r="AI9" s="27" t="n">
-        <v>61.81</v>
+        <v>65.87</v>
       </c>
       <c r="AJ9" s="27" t="n">
-        <v>-29.27</v>
+        <v>-23.4</v>
       </c>
       <c r="AK9" s="27" t="n">
-        <v>12.38</v>
+        <v>5.57</v>
       </c>
       <c r="AL9" s="27" t="n">
-        <v>62.89</v>
+        <v>62.99</v>
       </c>
       <c r="AM9" s="27" t="n">
-        <v>-30.53</v>
+        <v>-30.65</v>
       </c>
       <c r="AN9" s="27" t="n">
-        <v>14.45</v>
+        <v>15.57</v>
       </c>
       <c r="AO9" s="27" t="n">
-        <v>40.13</v>
+        <v>38.02</v>
       </c>
       <c r="AP9" s="27" t="n">
-        <v>-7.58</v>
+        <v>-14.61</v>
       </c>
       <c r="AQ9" s="27" t="n">
-        <v>-25.68</v>
+        <v>-19.04</v>
       </c>
       <c r="AR9" s="27" t="n">
-        <v>38.33</v>
+        <v>36.81</v>
       </c>
       <c r="AS9" s="27" t="n">
-        <v>-6.97</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="AT9" s="27" t="n">
-        <v>-29.5</v>
+        <v>-32.04</v>
       </c>
     </row>
     <row r="10">
@@ -11269,139 +11269,139 @@
         </is>
       </c>
       <c r="B10" s="27" t="n">
-        <v>46.5</v>
+        <v>44.57</v>
       </c>
       <c r="C10" s="27" t="n">
-        <v>33.5</v>
+        <v>29.32</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>16.26</v>
+        <v>11.24</v>
       </c>
       <c r="E10" s="27" t="n">
-        <v>45.15</v>
+        <v>42.51</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>34.19</v>
+        <v>30.41</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>15.56</v>
+        <v>8.57</v>
       </c>
       <c r="H10" s="27" t="n">
-        <v>46.89</v>
+        <v>44.31</v>
       </c>
       <c r="I10" s="27" t="n">
-        <v>33.61</v>
+        <v>29.28</v>
       </c>
       <c r="J10" s="27" t="n">
-        <v>15.02</v>
+        <v>5.61</v>
       </c>
       <c r="K10" s="27" t="n">
-        <v>60.75</v>
+        <v>62.64</v>
       </c>
       <c r="L10" s="27" t="n">
-        <v>-31.41</v>
+        <v>-30.76</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>14.64</v>
+        <v>13.42</v>
       </c>
       <c r="N10" s="27" t="n">
-        <v>58.41</v>
+        <v>56.66</v>
       </c>
       <c r="O10" s="27" t="n">
-        <v>-32.36</v>
+        <v>-32.32</v>
       </c>
       <c r="P10" s="27" t="n">
-        <v>16.44</v>
+        <v>19.89</v>
       </c>
       <c r="Q10" s="27" t="n">
-        <v>61.58</v>
+        <v>66.86</v>
       </c>
       <c r="R10" s="27" t="n">
-        <v>-28.83</v>
+        <v>-22.29</v>
       </c>
       <c r="S10" s="27" t="n">
-        <v>14.53</v>
+        <v>11.58</v>
       </c>
       <c r="T10" s="27" t="n">
-        <v>44.51</v>
+        <v>50.83</v>
       </c>
       <c r="U10" s="27" t="n">
-        <v>-6.68</v>
+        <v>-9.48</v>
       </c>
       <c r="V10" s="27" t="n">
-        <v>-29.48</v>
+        <v>-22.84</v>
       </c>
       <c r="W10" s="27" t="n">
-        <v>41.12</v>
+        <v>42.36</v>
       </c>
       <c r="X10" s="27" t="n">
-        <v>-4.69</v>
+        <v>-4.18</v>
       </c>
       <c r="Y10" s="27" t="n">
-        <v>-33.56</v>
+        <v>-34.47</v>
       </c>
       <c r="Z10" s="27" t="n">
-        <v>41.35</v>
+        <v>42.85</v>
       </c>
       <c r="AA10" s="27" t="n">
-        <v>-4.9</v>
+        <v>-3.8</v>
       </c>
       <c r="AB10" s="27" t="n">
-        <v>-33.95</v>
+        <v>-37.46</v>
       </c>
       <c r="AC10" s="27" t="n">
-        <v>50.09</v>
+        <v>51.9</v>
       </c>
       <c r="AD10" s="27" t="n">
-        <v>30.2</v>
+        <v>18.21</v>
       </c>
       <c r="AE10" s="27" t="n">
-        <v>15.42</v>
+        <v>1.55</v>
       </c>
       <c r="AF10" s="27" t="n">
-        <v>50.8</v>
+        <v>49.01</v>
       </c>
       <c r="AG10" s="27" t="n">
-        <v>33.33</v>
+        <v>30.4</v>
       </c>
       <c r="AH10" s="27" t="n">
-        <v>18.42</v>
+        <v>12.81</v>
       </c>
       <c r="AI10" s="27" t="n">
-        <v>60.93</v>
+        <v>63.21</v>
       </c>
       <c r="AJ10" s="27" t="n">
-        <v>-28.41</v>
+        <v>-20.79</v>
       </c>
       <c r="AK10" s="27" t="n">
-        <v>11.43</v>
+        <v>2.69</v>
       </c>
       <c r="AL10" s="27" t="n">
-        <v>62.95</v>
+        <v>63.17</v>
       </c>
       <c r="AM10" s="27" t="n">
-        <v>-30.48</v>
+        <v>-30.5</v>
       </c>
       <c r="AN10" s="27" t="n">
-        <v>14.75</v>
+        <v>16.48</v>
       </c>
       <c r="AO10" s="27" t="n">
-        <v>40.66</v>
+        <v>39.62</v>
       </c>
       <c r="AP10" s="27" t="n">
-        <v>-7.48</v>
+        <v>-14.31</v>
       </c>
       <c r="AQ10" s="27" t="n">
-        <v>-25.49</v>
+        <v>-18.46</v>
       </c>
       <c r="AR10" s="27" t="n">
-        <v>40.28</v>
+        <v>42.72</v>
       </c>
       <c r="AS10" s="27" t="n">
-        <v>-7.52</v>
+        <v>-10.53</v>
       </c>
       <c r="AT10" s="27" t="n">
-        <v>-28.47</v>
+        <v>-28.92</v>
       </c>
     </row>
     <row r="11">
@@ -11411,139 +11411,139 @@
         </is>
       </c>
       <c r="B11" s="27" t="n">
-        <v>46.49</v>
+        <v>44.54</v>
       </c>
       <c r="C11" s="27" t="n">
-        <v>33.2</v>
+        <v>28.41</v>
       </c>
       <c r="D11" s="27" t="n">
-        <v>16.02</v>
+        <v>10.51</v>
       </c>
       <c r="E11" s="27" t="n">
-        <v>45.06</v>
+        <v>42.24</v>
       </c>
       <c r="F11" s="27" t="n">
-        <v>33.89</v>
+        <v>29.5</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>15.18</v>
+        <v>7.42</v>
       </c>
       <c r="H11" s="27" t="n">
-        <v>46.84</v>
+        <v>44.16</v>
       </c>
       <c r="I11" s="27" t="n">
-        <v>33.49</v>
+        <v>28.92</v>
       </c>
       <c r="J11" s="27" t="n">
-        <v>14.93</v>
+        <v>5.34</v>
       </c>
       <c r="K11" s="27" t="n">
-        <v>60.94</v>
+        <v>63.22</v>
       </c>
       <c r="L11" s="27" t="n">
-        <v>-31.38</v>
+        <v>-30.67</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>15.31</v>
+        <v>15.45</v>
       </c>
       <c r="N11" s="27" t="n">
-        <v>58.23</v>
+        <v>56.12</v>
       </c>
       <c r="O11" s="27" t="n">
-        <v>-31.76</v>
+        <v>-30.5</v>
       </c>
       <c r="P11" s="27" t="n">
-        <v>16.69</v>
+        <v>20.65</v>
       </c>
       <c r="Q11" s="27" t="n">
-        <v>60.53</v>
+        <v>63.68</v>
       </c>
       <c r="R11" s="27" t="n">
-        <v>-29.37</v>
+        <v>-23.93</v>
       </c>
       <c r="S11" s="27" t="n">
-        <v>13.3</v>
+        <v>7.86</v>
       </c>
       <c r="T11" s="27" t="n">
-        <v>45.24</v>
+        <v>53.04</v>
       </c>
       <c r="U11" s="27" t="n">
-        <v>-7.35</v>
+        <v>-11.51</v>
       </c>
       <c r="V11" s="27" t="n">
-        <v>-30.59</v>
+        <v>-26.2</v>
       </c>
       <c r="W11" s="27" t="n">
-        <v>40.88</v>
+        <v>41.63</v>
       </c>
       <c r="X11" s="27" t="n">
-        <v>-4.27</v>
+        <v>-2.91</v>
       </c>
       <c r="Y11" s="27" t="n">
-        <v>-34.09</v>
+        <v>-36.08</v>
       </c>
       <c r="Z11" s="27" t="n">
-        <v>41.79</v>
+        <v>44.19</v>
       </c>
       <c r="AA11" s="27" t="n">
-        <v>-5.46</v>
+        <v>-5.5</v>
       </c>
       <c r="AB11" s="27" t="n">
-        <v>-31.7</v>
+        <v>-30.64</v>
       </c>
       <c r="AC11" s="27" t="n">
-        <v>50.29</v>
+        <v>52.5</v>
       </c>
       <c r="AD11" s="27" t="n">
-        <v>29.76</v>
+        <v>16.88</v>
       </c>
       <c r="AE11" s="27" t="n">
-        <v>15.82</v>
+        <v>2.76</v>
       </c>
       <c r="AF11" s="27" t="n">
-        <v>50.8</v>
+        <v>49.01</v>
       </c>
       <c r="AG11" s="27" t="n">
-        <v>33.12</v>
+        <v>29.77</v>
       </c>
       <c r="AH11" s="27" t="n">
-        <v>18.79</v>
+        <v>13.93</v>
       </c>
       <c r="AI11" s="27" t="n">
-        <v>61.75</v>
+        <v>65.69</v>
       </c>
       <c r="AJ11" s="27" t="n">
-        <v>-28.33</v>
+        <v>-20.55</v>
       </c>
       <c r="AK11" s="27" t="n">
-        <v>11.74</v>
+        <v>3.63</v>
       </c>
       <c r="AL11" s="27" t="n">
-        <v>62.95</v>
+        <v>63.17</v>
       </c>
       <c r="AM11" s="27" t="n">
-        <v>-30.41</v>
+        <v>-30.29</v>
       </c>
       <c r="AN11" s="27" t="n">
-        <v>14.35</v>
+        <v>15.26</v>
       </c>
       <c r="AO11" s="27" t="n">
-        <v>40.12</v>
+        <v>37.99</v>
       </c>
       <c r="AP11" s="27" t="n">
-        <v>-6.92</v>
+        <v>-12.61</v>
       </c>
       <c r="AQ11" s="27" t="n">
-        <v>-26.43</v>
+        <v>-21.31</v>
       </c>
       <c r="AR11" s="27" t="n">
-        <v>40.47</v>
+        <v>43.29</v>
       </c>
       <c r="AS11" s="27" t="n">
-        <v>-7.68</v>
+        <v>-11.01</v>
       </c>
       <c r="AT11" s="27" t="n">
-        <v>-28.2</v>
+        <v>-28.1</v>
       </c>
     </row>
     <row r="12">
@@ -11553,139 +11553,139 @@
         </is>
       </c>
       <c r="B12" s="26" t="n">
-        <v>46.44</v>
+        <v>44.39</v>
       </c>
       <c r="C12" s="26" t="n">
-        <v>32.86</v>
+        <v>27.38</v>
       </c>
       <c r="D12" s="26" t="n">
-        <v>15.79</v>
+        <v>9.82</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>45.2</v>
+        <v>42.66</v>
       </c>
       <c r="F12" s="26" t="n">
-        <v>33.89</v>
+        <v>29.5</v>
       </c>
       <c r="G12" s="26" t="n">
-        <v>14.72</v>
+        <v>6.03</v>
       </c>
       <c r="H12" s="26" t="n">
-        <v>46.71</v>
+        <v>43.76</v>
       </c>
       <c r="I12" s="26" t="n">
-        <v>33.37</v>
+        <v>28.56</v>
       </c>
       <c r="J12" s="26" t="n">
-        <v>14.77</v>
+        <v>4.86</v>
       </c>
       <c r="K12" s="26" t="n">
-        <v>60.39</v>
+        <v>61.55</v>
       </c>
       <c r="L12" s="26" t="n">
-        <v>-31.89</v>
+        <v>-32.22</v>
       </c>
       <c r="M12" s="26" t="n">
         <v>15.24</v>
       </c>
       <c r="N12" s="26" t="n">
-        <v>57.3</v>
+        <v>53.3</v>
       </c>
       <c r="O12" s="26" t="n">
-        <v>-31.27</v>
+        <v>-29.02</v>
       </c>
       <c r="P12" s="26" t="n">
-        <v>16.52</v>
+        <v>20.14</v>
       </c>
       <c r="Q12" s="26" t="n">
-        <v>59.42</v>
+        <v>60.31</v>
       </c>
       <c r="R12" s="26" t="n">
-        <v>-29.89</v>
+        <v>-25.5</v>
       </c>
       <c r="S12" s="26" t="n">
-        <v>10.83</v>
+        <v>0.37</v>
       </c>
       <c r="T12" s="26" t="n">
-        <v>42.53</v>
+        <v>44.83</v>
       </c>
       <c r="U12" s="26" t="n">
-        <v>-6.95</v>
+        <v>-10.3</v>
       </c>
       <c r="V12" s="26" t="n">
-        <v>-33.55</v>
+        <v>-35.18</v>
       </c>
       <c r="W12" s="26" t="n">
-        <v>40.86</v>
+        <v>41.57</v>
       </c>
       <c r="X12" s="26" t="n">
-        <v>-4.23</v>
+        <v>-2.79</v>
       </c>
       <c r="Y12" s="26" t="n">
-        <v>-33.39</v>
+        <v>-33.96</v>
       </c>
       <c r="Z12" s="26" t="n">
-        <v>42.07</v>
+        <v>45.04</v>
       </c>
       <c r="AA12" s="26" t="n">
-        <v>-5.18</v>
+        <v>-4.65</v>
       </c>
       <c r="AB12" s="26" t="n">
-        <v>-28.84</v>
+        <v>-21.97</v>
       </c>
       <c r="AC12" s="26" t="n">
-        <v>50.38</v>
+        <v>52.78</v>
       </c>
       <c r="AD12" s="26" t="n">
-        <v>29.8</v>
+        <v>17</v>
       </c>
       <c r="AE12" s="26" t="n">
-        <v>17.36</v>
+        <v>7.43</v>
       </c>
       <c r="AF12" s="26" t="n">
-        <v>50.81</v>
+        <v>49.04</v>
       </c>
       <c r="AG12" s="26" t="n">
-        <v>32.37</v>
+        <v>27.49</v>
       </c>
       <c r="AH12" s="26" t="n">
-        <v>19.25</v>
+        <v>15.33</v>
       </c>
       <c r="AI12" s="26" t="n">
-        <v>62.98</v>
+        <v>69.42</v>
       </c>
       <c r="AJ12" s="26" t="n">
-        <v>-29.39</v>
+        <v>-23.76</v>
       </c>
       <c r="AK12" s="26" t="n">
-        <v>12.93</v>
+        <v>7.24</v>
       </c>
       <c r="AL12" s="26" t="n">
-        <v>63.17</v>
+        <v>63.84</v>
       </c>
       <c r="AM12" s="26" t="n">
-        <v>-30.17</v>
+        <v>-29.56</v>
       </c>
       <c r="AN12" s="26" t="n">
-        <v>13.69</v>
+        <v>13.26</v>
       </c>
       <c r="AO12" s="26" t="n">
-        <v>38.47</v>
+        <v>32.99</v>
       </c>
       <c r="AP12" s="26" t="n">
-        <v>-5.18</v>
+        <v>-7.33</v>
       </c>
       <c r="AQ12" s="26" t="n">
-        <v>-28.45</v>
+        <v>-27.43</v>
       </c>
       <c r="AR12" s="26" t="n">
-        <v>40.72</v>
+        <v>44.05</v>
       </c>
       <c r="AS12" s="26" t="n">
-        <v>-6.72</v>
+        <v>-8.1</v>
       </c>
       <c r="AT12" s="26" t="n">
-        <v>-29.82</v>
+        <v>-33.01</v>
       </c>
     </row>
     <row r="13">
